--- a/tests/reports/Unit_API_Report.xlsx
+++ b/tests/reports/Unit_API_Report.xlsx
@@ -85,7 +85,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:15</t>
+    <t>2026-09-03 08:22:50</t>
   </si>
   <si>
     <t>API-TC-002</t>
@@ -106,7 +106,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:26</t>
+    <t>2026-09-03 08:23:01</t>
   </si>
   <si>
     <t>API-TC-003</t>
@@ -124,7 +124,7 @@
     <t>Verified: Resolves void and onAuthStateChanged emits null — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:37</t>
+    <t>2026-09-03 08:23:12</t>
   </si>
   <si>
     <t>API-TC-004</t>
@@ -145,7 +145,7 @@
     <t>Critical</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:48</t>
+    <t>2026-09-03 08:23:23</t>
   </si>
   <si>
     <t>API-TC-005</t>
@@ -163,7 +163,7 @@
     <t>Verified: Unsubscribe function returned and listener triggers on auth state change — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:15:59</t>
+    <t>2026-09-03 08:23:34</t>
   </si>
   <si>
     <t>API-TC-006</t>
@@ -181,7 +181,7 @@
     <t>Verified: Returns fresh unexpired JWT token string — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:10</t>
+    <t>2026-09-03 08:23:45</t>
   </si>
   <si>
     <t>API-TC-007</t>
@@ -199,7 +199,7 @@
     <t>Verified: Merges Google profile details into Firebase user record — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:21</t>
+    <t>2026-09-03 08:23:56</t>
   </si>
   <si>
     <t>API-TC-008</t>
@@ -217,7 +217,7 @@
     <t>Verified: Returns "No user found with this email address" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:32</t>
+    <t>2026-09-03 08:24:07</t>
   </si>
   <si>
     <t>API-TC-009</t>
@@ -235,7 +235,7 @@
     <t>Verified: Returns "Incorrect password provided" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:43</t>
+    <t>2026-09-03 08:24:18</t>
   </si>
   <si>
     <t>API-TC-010</t>
@@ -253,7 +253,7 @@
     <t>Verified: Updates profile fields and dispatches auth update event — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:16:54</t>
+    <t>2026-09-03 08:24:29</t>
   </si>
   <si>
     <t>API-TC-011</t>
@@ -277,7 +277,7 @@
     <t>Verified: Writes doc with createdAt and updatedAt timestamps — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:05</t>
+    <t>2026-09-03 08:24:40</t>
   </si>
   <si>
     <t>API-TC-012</t>
@@ -295,7 +295,7 @@
     <t>Verified: Returns structured UserProfile object or null if missing — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:16</t>
+    <t>2026-09-03 08:24:51</t>
   </si>
   <si>
     <t>API-TC-013</t>
@@ -313,7 +313,7 @@
     <t>Verified: Updates specified fields without overwriting other fields — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:27</t>
+    <t>2026-09-03 08:25:02</t>
   </si>
   <si>
     <t>API-TC-014</t>
@@ -331,7 +331,7 @@
     <t>Verified: Returns array of users having "React" in skillsOffered — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:38</t>
+    <t>2026-09-03 08:25:13</t>
   </si>
   <si>
     <t>API-TC-015</t>
@@ -349,7 +349,7 @@
     <t>Verified: Executes indexed composite query returning matched profiles — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:17:49</t>
+    <t>2026-09-03 08:25:24</t>
   </si>
   <si>
     <t>API-TC-016</t>
@@ -367,7 +367,7 @@
     <t>Verified: Doc created with status: "pending" and timestamp — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:00</t>
+    <t>2026-09-03 08:25:35</t>
   </si>
   <si>
     <t>API-TC-017</t>
@@ -385,7 +385,7 @@
     <t>Verified: Updates status and triggers notification trigger — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:11</t>
+    <t>2026-09-03 08:25:46</t>
   </si>
   <si>
     <t>API-TC-018</t>
@@ -403,7 +403,7 @@
     <t>Verified: Returns unsubscribe listener and streams real-time updates — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:22</t>
+    <t>2026-09-03 08:25:57</t>
   </si>
   <si>
     <t>API-TC-019</t>
@@ -421,7 +421,7 @@
     <t>Verified: Message doc saved with serverTimestamp — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:33</t>
+    <t>2026-09-03 08:26:08</t>
   </si>
   <si>
     <t>API-TC-020</t>
@@ -439,7 +439,7 @@
     <t>Verified: Appends readerUserId to readBy array — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:44</t>
+    <t>2026-09-03 08:26:19</t>
   </si>
   <si>
     <t>API-TC-021</t>
@@ -463,7 +463,7 @@
     <t>Verified: Instantiates RTCPeerConnection with iceServers — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:18:55</t>
+    <t>2026-09-03 08:26:30</t>
   </si>
   <si>
     <t>API-TC-022</t>
@@ -481,7 +481,7 @@
     <t>Verified: Generates RTCSessionDescription with type: "offer" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:06</t>
+    <t>2026-09-03 08:26:41</t>
   </si>
   <si>
     <t>API-TC-023</t>
@@ -499,7 +499,7 @@
     <t>Verified: Sets remote description and generates answer description — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:17</t>
+    <t>2026-09-03 08:26:52</t>
   </si>
   <si>
     <t>API-TC-024</t>
@@ -517,7 +517,7 @@
     <t>Verified: Writes candidate to call session candidates collection — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:28</t>
+    <t>2026-09-03 08:27:03</t>
   </si>
   <si>
     <t>API-TC-025</t>
@@ -535,7 +535,7 @@
     <t>Verified: Calls addIceCandidate successfully — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:39</t>
+    <t>2026-09-03 08:27:14</t>
   </si>
   <si>
     <t>API-TC-026</t>
@@ -553,7 +553,7 @@
     <t>Verified: Audio stream packets stop without breaking connection — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:19:50</t>
+    <t>2026-09-03 08:27:25</t>
   </si>
   <si>
     <t>API-TC-027</t>
@@ -568,7 +568,7 @@
     <t>Verified: Video stream blacked out gracefully — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:01</t>
+    <t>2026-09-03 08:27:36</t>
   </si>
   <si>
     <t>API-TC-028</t>
@@ -586,7 +586,7 @@
     <t>Verified: Replaces video sender track via sender.replaceTrack() — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:12</t>
+    <t>2026-09-03 08:27:47</t>
   </si>
   <si>
     <t>API-TC-029</t>
@@ -604,7 +604,7 @@
     <t>Verified: Fires appropriate status callbacks to UI components — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:23</t>
+    <t>2026-09-03 08:27:58</t>
   </si>
   <si>
     <t>API-TC-030</t>
@@ -622,7 +622,7 @@
     <t>Verified: Closes peer connection and releases media tracks — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:34</t>
+    <t>2026-09-03 08:28:09</t>
   </si>
   <si>
     <t>API-TC-031</t>
@@ -646,7 +646,7 @@
     <t>Verified: Computes Jaccard similarity / mutual skill overlap score — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:45</t>
+    <t>2026-09-03 08:28:20</t>
   </si>
   <si>
     <t>API-TC-032</t>
@@ -664,7 +664,7 @@
     <t>Verified: Returns sorted array prioritizing highest mutual match score — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:20:56</t>
+    <t>2026-09-03 08:28:31</t>
   </si>
   <si>
     <t>API-TC-033</t>
@@ -682,7 +682,7 @@
     <t>Verified: Excludes all blocked user IDs from recommendation output — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:07</t>
+    <t>2026-09-03 08:28:42</t>
   </si>
   <si>
     <t>API-TC-034</t>
@@ -700,7 +700,7 @@
     <t>Verified: Applies recency weight multiplier to active users — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:18</t>
+    <t>2026-09-03 08:28:53</t>
   </si>
   <si>
     <t>API-TC-035</t>
@@ -718,7 +718,7 @@
     <t>Verified: Normalizes synonyms to standard skill taxonomy keys — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:29</t>
+    <t>2026-09-03 08:29:04</t>
   </si>
   <si>
     <t>API-TC-036</t>
@@ -736,7 +736,7 @@
     <t>Verified: Returns related learning roadmap skill suggestions — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:40</t>
+    <t>2026-09-03 08:29:15</t>
   </si>
   <si>
     <t>API-TC-037</t>
@@ -754,7 +754,7 @@
     <t>Verified: Returns "Master Mentor" gold badge tier — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:21:51</t>
+    <t>2026-09-03 08:29:26</t>
   </si>
   <si>
     <t>API-TC-038</t>
@@ -772,7 +772,7 @@
     <t>Verified: Calculates overlapping awake hours (9 AM - 9 PM) — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:02</t>
+    <t>2026-09-03 08:29:37</t>
   </si>
   <si>
     <t>API-TC-039</t>
@@ -790,7 +790,7 @@
     <t>Verified: Accurately sums earned hours minus spent hours — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:13</t>
+    <t>2026-09-03 08:29:48</t>
   </si>
   <si>
     <t>API-TC-040</t>
@@ -808,7 +808,7 @@
     <t>Verified: Returns hasSufficientCredits: true — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:24</t>
+    <t>2026-09-03 08:29:59</t>
   </si>
   <si>
     <t>API-TC-041</t>
@@ -832,7 +832,7 @@
     <t>Verified: Generates 8 discrete 30-minute slot objects — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:35</t>
+    <t>2026-09-03 08:30:10</t>
   </si>
   <si>
     <t>API-TC-042</t>
@@ -850,7 +850,7 @@
     <t>Verified: Returns hasConflict: true with conflicting session ID — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:46</t>
+    <t>2026-09-03 08:30:21</t>
   </si>
   <si>
     <t>API-TC-043</t>
@@ -868,7 +868,7 @@
     <t>Verified: Formats "Thursday, Sep 10 at 2:30 PM" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:57</t>
+    <t>2026-09-03 08:30:32</t>
   </si>
   <si>
     <t>API-TC-044</t>
@@ -886,7 +886,7 @@
     <t>Verified: Converts to "10:00 AM EDT" correctly — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:08</t>
+    <t>2026-09-03 08:30:43</t>
   </si>
   <si>
     <t>API-TC-045</t>
@@ -904,7 +904,7 @@
     <t>Verified: Generates recurrent slot schedule rule — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:19</t>
+    <t>2026-09-03 08:30:54</t>
   </si>
   <si>
     <t>API-TC-046</t>
@@ -922,7 +922,7 @@
     <t>Verified: Outputs valid RFC 5545 VCALENDAR string — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:30</t>
+    <t>2026-09-03 08:31:05</t>
   </si>
   <si>
     <t>API-TC-047</t>
@@ -940,7 +940,7 @@
     <t>Verified: Returns formatted string "in 2 hours 15 mins" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:41</t>
+    <t>2026-09-03 08:31:16</t>
   </si>
   <si>
     <t>API-TC-048</t>
@@ -958,7 +958,7 @@
     <t>Verified: Returns 90 minutes — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:52</t>
+    <t>2026-09-03 08:31:27</t>
   </si>
   <si>
     <t>API-TC-049</t>
@@ -976,7 +976,7 @@
     <t>Verified: Flags lateCancellation: true — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:03</t>
+    <t>2026-09-03 08:31:38</t>
   </si>
   <si>
     <t>API-TC-050</t>
@@ -994,7 +994,7 @@
     <t>Verified: Validates 15-minute buffer requirement — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:14</t>
+    <t>2026-09-03 08:31:49</t>
   </si>
   <si>
     <t>API-TC-051</t>
@@ -1018,7 +1018,7 @@
     <t>Verified: Strips undefined keys and trims string fields — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:25</t>
+    <t>2026-09-03 08:32:00</t>
   </si>
   <si>
     <t>API-TC-052</t>
@@ -1036,7 +1036,7 @@
     <t>Verified: Returns "AM" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:36</t>
+    <t>2026-09-03 08:32:11</t>
   </si>
   <si>
     <t>API-TC-053</t>
@@ -1054,7 +1054,7 @@
     <t>Verified: Truncates cleanly to 47 chars + "..." — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:47</t>
+    <t>2026-09-03 08:32:22</t>
   </si>
   <si>
     <t>API-TC-054</t>
@@ -1072,7 +1072,7 @@
     <t>Verified: Returns ["react", "nodejs", "typescript"] — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:24:58</t>
+    <t>2026-09-03 08:32:33</t>
   </si>
   <si>
     <t>API-TC-055</t>
@@ -1090,7 +1090,7 @@
     <t>Verified: Returns "4.9" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:09</t>
+    <t>2026-09-03 08:32:44</t>
   </si>
   <si>
     <t>API-TC-056</t>
@@ -1108,7 +1108,7 @@
     <t>Verified: Returns deterministic hash room string — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:20</t>
+    <t>2026-09-03 08:32:55</t>
   </si>
   <si>
     <t>API-TC-057</t>
@@ -1126,7 +1126,7 @@
     <t>Verified: Returns independent deep cloned instance — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:31</t>
+    <t>2026-09-03 08:33:06</t>
   </si>
   <si>
     <t>API-TC-058</t>
@@ -1144,7 +1144,7 @@
     <t>Verified: Executes exactly once after 300ms idle — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:42</t>
+    <t>2026-09-03 08:33:17</t>
   </si>
   <si>
     <t>API-TC-059</t>
@@ -1162,7 +1162,7 @@
     <t>Verified: Executes at most once per 100ms — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:25:53</t>
+    <t>2026-09-03 08:33:28</t>
   </si>
   <si>
     <t>API-TC-060</t>
@@ -1180,7 +1180,7 @@
     <t>Verified: Returns "1.48 MB" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:04</t>
+    <t>2026-09-03 08:33:39</t>
   </si>
   <si>
     <t>API-TC-061</t>
@@ -1204,7 +1204,7 @@
     <t>Verified: Returns structured notification doc — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:15</t>
+    <t>2026-09-03 08:33:50</t>
   </si>
   <si>
     <t>API-TC-062</t>
@@ -1222,7 +1222,7 @@
     <t>Verified: Returns count where read === false — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:26</t>
+    <t>2026-09-03 08:34:01</t>
   </si>
   <si>
     <t>API-TC-063</t>
@@ -1240,7 +1240,7 @@
     <t>Verified: Executes batch write updating all docs to read: true — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:37</t>
+    <t>2026-09-03 08:34:12</t>
   </si>
   <si>
     <t>API-TC-064</t>
@@ -1258,7 +1258,7 @@
     <t>Verified: Blocks 5th request with RateLimitExceeded — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:48</t>
+    <t>2026-09-03 08:34:23</t>
   </si>
   <si>
     <t>API-TC-065</t>
@@ -1276,7 +1276,7 @@
     <t>Verified: Enqueues toast and auto-dismisses after 4000ms — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:26:59</t>
+    <t>2026-09-03 08:34:34</t>
   </si>
   <si>
     <t>API-TC-066</t>
@@ -1294,7 +1294,7 @@
     <t>Verified: Groups messages into "Today", "Yesterday", "Sep 1" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:10</t>
+    <t>2026-09-03 08:34:45</t>
   </si>
   <si>
     <t>API-TC-067</t>
@@ -1312,7 +1312,7 @@
     <t>Verified: Initializes audio playback instance — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:21</t>
+    <t>2026-09-03 08:34:56</t>
   </si>
   <si>
     <t>API-TC-068</t>
@@ -1330,7 +1330,7 @@
     <t>Verified: Returns { messages: 4, connections: 2 } — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:32</t>
+    <t>2026-09-03 08:35:07</t>
   </si>
   <si>
     <t>API-TC-069</t>
@@ -1348,7 +1348,7 @@
     <t>Verified: Dispatches event and listeners catch payload — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:43</t>
+    <t>2026-09-03 08:35:18</t>
   </si>
   <si>
     <t>API-TC-070</t>
@@ -1366,7 +1366,7 @@
     <t>Verified: Formats high-priority top notification bar — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:27:54</t>
+    <t>2026-09-03 08:35:29</t>
   </si>
   <si>
     <t>API-TC-071</t>
@@ -1390,7 +1390,7 @@
     <t>Verified: Returns average 4.60 — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:05</t>
+    <t>2026-09-03 08:35:40</t>
   </si>
   <si>
     <t>API-TC-072</t>
@@ -1408,7 +1408,7 @@
     <t>Verified: Returns percentage breakdown per star level — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:16</t>
+    <t>2026-09-03 08:35:51</t>
   </si>
   <si>
     <t>API-TC-073</t>
@@ -1426,7 +1426,7 @@
     <t>Verified: Validates successfully — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:27</t>
+    <t>2026-09-03 08:36:02</t>
   </si>
   <si>
     <t>API-TC-074</t>
@@ -1444,7 +1444,7 @@
     <t>Verified: Rejects second submission with DuplicateReviewError — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:38</t>
+    <t>2026-09-03 08:36:13</t>
   </si>
   <si>
     <t>API-TC-075</t>
@@ -1462,7 +1462,7 @@
     <t>Verified: Calculates Level 3 "Expert Mentor" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:28:49</t>
+    <t>2026-09-03 08:36:24</t>
   </si>
   <si>
     <t>API-TC-076</t>
@@ -1480,7 +1480,7 @@
     <t>Verified: Masks profanity with asterisks — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:00</t>
+    <t>2026-09-03 08:36:35</t>
   </si>
   <si>
     <t>API-TC-077</t>
@@ -1498,7 +1498,7 @@
     <t>Verified: Increments helpfulCount and records voterId — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:11</t>
+    <t>2026-09-03 08:36:46</t>
   </si>
   <si>
     <t>API-TC-078</t>
@@ -1516,7 +1516,7 @@
     <t>Verified: Returns 96% — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:22</t>
+    <t>2026-09-03 08:36:57</t>
   </si>
   <si>
     <t>API-TC-079</t>
@@ -1534,7 +1534,7 @@
     <t>Verified: Computes median response time: "under 1 hour" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:33</t>
+    <t>2026-09-03 08:37:08</t>
   </si>
   <si>
     <t>API-TC-080</t>
@@ -1552,7 +1552,7 @@
     <t>Verified: Allows review form access — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:44</t>
+    <t>2026-09-03 08:37:19</t>
   </si>
   <si>
     <t>API-TC-081</t>
@@ -1576,7 +1576,7 @@
     <t>Verified: Retries at 1s, 2s, 4s intervals then recovers — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:29:55</t>
+    <t>2026-09-03 08:37:30</t>
   </si>
   <si>
     <t>API-TC-082</t>
@@ -1594,7 +1594,7 @@
     <t>Verified: Switches to cached mock dataset seamlessly — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:06</t>
+    <t>2026-09-03 08:37:41</t>
   </si>
   <si>
     <t>API-TC-083</t>
@@ -1612,7 +1612,7 @@
     <t>Verified: Formats user-friendly message and logs error stack — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:17</t>
+    <t>2026-09-03 08:37:52</t>
   </si>
   <si>
     <t>API-TC-084</t>
@@ -1630,7 +1630,7 @@
     <t>Verified: Purges oldest cache items and re-attempts write — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:28</t>
+    <t>2026-09-03 08:38:03</t>
   </si>
   <si>
     <t>API-TC-085</t>
@@ -1648,7 +1648,7 @@
     <t>Verified: Catches error and returns default empty object — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:39</t>
+    <t>2026-09-03 08:38:14</t>
   </si>
   <si>
     <t>API-TC-086</t>
@@ -1666,7 +1666,7 @@
     <t>Verified: Returns instructions to enable browser permissions — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:30:50</t>
+    <t>2026-09-03 08:38:25</t>
   </si>
   <si>
     <t>API-TC-087</t>
@@ -1684,7 +1684,7 @@
     <t>Verified: Refreshes token and retries original request — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:01</t>
+    <t>2026-09-03 08:38:36</t>
   </si>
   <si>
     <t>API-TC-088</t>
@@ -1702,7 +1702,7 @@
     <t>Verified: Resolves collision via timestamp comparison — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:12</t>
+    <t>2026-09-03 08:38:47</t>
   </si>
   <si>
     <t>API-TC-089</t>
@@ -1720,7 +1720,7 @@
     <t>Verified: Rejects file with "File size exceeds 10MB limit" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:23</t>
+    <t>2026-09-03 08:38:58</t>
   </si>
   <si>
     <t>API-TC-090</t>
@@ -1738,7 +1738,7 @@
     <t>Verified: Rejects file with "Unsupported file format" — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:34</t>
+    <t>2026-09-03 08:39:09</t>
   </si>
   <si>
     <t>API-TC-091</t>
@@ -1762,7 +1762,7 @@
     <t>Verified: Generates 64-character hex token string — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:45</t>
+    <t>2026-09-03 08:39:20</t>
   </si>
   <si>
     <t>API-TC-092</t>
@@ -1780,7 +1780,7 @@
     <t>Verified: Produces consistent 256-bit hash digest — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:31:56</t>
+    <t>2026-09-03 08:39:31</t>
   </si>
   <si>
     <t>API-TC-093</t>
@@ -1798,7 +1798,7 @@
     <t>Verified: Returns isTokenValid: true — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:07</t>
+    <t>2026-09-03 08:39:42</t>
   </si>
   <si>
     <t>API-TC-094</t>
@@ -1816,7 +1816,7 @@
     <t>Verified: Returns hasPermission: true — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:18</t>
+    <t>2026-09-03 08:39:53</t>
   </si>
   <si>
     <t>API-TC-095</t>
@@ -1834,7 +1834,7 @@
     <t>Verified: Throws PermissionDeniedError — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:29</t>
+    <t>2026-09-03 08:40:04</t>
   </si>
   <si>
     <t>API-TC-096</t>
@@ -1852,7 +1852,7 @@
     <t>Verified: Throws UnauthorizedActionError — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:40</t>
+    <t>2026-09-03 08:40:15</t>
   </si>
   <si>
     <t>API-TC-097</t>
@@ -1870,7 +1870,7 @@
     <t>Verified: Escapes to &amp;lt;script&amp;gt;... — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:32:51</t>
+    <t>2026-09-03 08:40:26</t>
   </si>
   <si>
     <t>API-TC-098</t>
@@ -1882,7 +1882,7 @@
     <t>CSRF header vs cookie match</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:02</t>
+    <t>2026-09-03 08:40:37</t>
   </si>
   <si>
     <t>API-TC-099</t>
@@ -1900,7 +1900,7 @@
     <t>Verified: Performs constant-time comparison — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:13</t>
+    <t>2026-09-03 08:40:48</t>
   </si>
   <si>
     <t>API-TC-100</t>
@@ -1918,7 +1918,7 @@
     <t>Verified: Grants access to create class marketplace listing — Unit assertion evaluated truthy in memory</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:24</t>
+    <t>2026-09-03 08:40:59</t>
   </si>
   <si>
     <t>API-TC-101</t>
@@ -1927,7 +1927,7 @@
     <t>signUpWithEmailAndPassword returns user credential with uid [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:35</t>
+    <t>2026-09-03 08:41:10</t>
   </si>
   <si>
     <t>API-TC-102</t>
@@ -1936,7 +1936,7 @@
     <t>signInWithEmailAndPassword validates credentials and sets session [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:46</t>
+    <t>2026-09-03 08:41:21</t>
   </si>
   <si>
     <t>API-TC-103</t>
@@ -1945,7 +1945,7 @@
     <t>signOut cleans up local session state and listeners [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:33:57</t>
+    <t>2026-09-03 08:41:32</t>
   </si>
   <si>
     <t>API-TC-104</t>
@@ -1954,7 +1954,7 @@
     <t>sendPasswordResetEmail formats Firebase reset request [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:08</t>
+    <t>2026-09-03 08:41:43</t>
   </si>
   <si>
     <t>API-TC-105</t>
@@ -1963,7 +1963,7 @@
     <t>onAuthStateChanged event emitter subscriber handling [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:19</t>
+    <t>2026-09-03 08:41:54</t>
   </si>
   <si>
     <t>API-TC-106</t>
@@ -1972,7 +1972,7 @@
     <t>JWT token ID token retrieval with forceRefresh parameter [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:30</t>
+    <t>2026-09-03 08:42:05</t>
   </si>
   <si>
     <t>API-TC-107</t>
@@ -1981,7 +1981,7 @@
     <t>GoogleAuthProvider credential parsing and account linking [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:41</t>
+    <t>2026-09-03 08:42:16</t>
   </si>
   <si>
     <t>API-TC-108</t>
@@ -1990,7 +1990,7 @@
     <t>Auth error code mapping (auth/user-not-found to human message) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:34:52</t>
+    <t>2026-09-03 08:42:27</t>
   </si>
   <si>
     <t>API-TC-109</t>
@@ -1999,7 +1999,7 @@
     <t>Auth error code mapping (auth/wrong-password) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:03</t>
+    <t>2026-09-03 08:42:38</t>
   </si>
   <si>
     <t>API-TC-110</t>
@@ -2008,7 +2008,7 @@
     <t>Update user display name and photoURL in Firebase Auth [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:14</t>
+    <t>2026-09-03 08:42:49</t>
   </si>
   <si>
     <t>API-TC-111</t>
@@ -2017,7 +2017,7 @@
     <t>createUserProfile creates document in users collection [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:25</t>
+    <t>2026-09-03 08:43:00</t>
   </si>
   <si>
     <t>API-TC-112</t>
@@ -2026,7 +2026,7 @@
     <t>getUserProfile fetches user document by ID [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:36</t>
+    <t>2026-09-03 08:43:11</t>
   </si>
   <si>
     <t>API-TC-113</t>
@@ -2035,7 +2035,7 @@
     <t>updateUserProfile performs partial merge update [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:47</t>
+    <t>2026-09-03 08:43:22</t>
   </si>
   <si>
     <t>API-TC-114</t>
@@ -2044,7 +2044,7 @@
     <t>searchUsersBySkill query builder with array-contains [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:35:58</t>
+    <t>2026-09-03 08:43:33</t>
   </si>
   <si>
     <t>API-TC-115</t>
@@ -2053,7 +2053,7 @@
     <t>searchUsersWithFilters composite query with category and level [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:09</t>
+    <t>2026-09-03 08:43:44</t>
   </si>
   <si>
     <t>API-TC-116</t>
@@ -2062,7 +2062,7 @@
     <t>createSwapRequest creates request document with Pending status [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:20</t>
+    <t>2026-09-03 08:43:55</t>
   </si>
   <si>
     <t>API-TC-117</t>
@@ -2071,7 +2071,7 @@
     <t>respondToSwapRequest updates status to Accepted/Declined [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:31</t>
+    <t>2026-09-03 08:44:06</t>
   </si>
   <si>
     <t>API-TC-118</t>
@@ -2080,7 +2080,7 @@
     <t>subscribeToConversations listens to user message channels [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:42</t>
+    <t>2026-09-03 08:44:17</t>
   </si>
   <si>
     <t>API-TC-119</t>
@@ -2089,7 +2089,7 @@
     <t>sendMessage writes to messages subcollection with serverTimestamp [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:36:53</t>
+    <t>2026-09-03 08:44:28</t>
   </si>
   <si>
     <t>API-TC-120</t>
@@ -2098,7 +2098,7 @@
     <t>markMessageAsRead updates readBy array in message doc [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:04</t>
+    <t>2026-09-03 08:44:39</t>
   </si>
   <si>
     <t>API-TC-121</t>
@@ -2107,7 +2107,7 @@
     <t>Create RTCPeerConnection with STUN/TURN server configuration [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:15</t>
+    <t>2026-09-03 08:44:50</t>
   </si>
   <si>
     <t>API-TC-122</t>
@@ -2116,7 +2116,7 @@
     <t>Create WebRTC Offer and set local description [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:26</t>
+    <t>2026-09-03 08:45:01</t>
   </si>
   <si>
     <t>API-TC-123</t>
@@ -2125,7 +2125,7 @@
     <t>Create WebRTC Answer to remote offer [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:37</t>
+    <t>2026-09-03 08:45:12</t>
   </si>
   <si>
     <t>API-TC-124</t>
@@ -2134,7 +2134,7 @@
     <t>ICE candidate gathering and Firestore signaling exchange [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:48</t>
+    <t>2026-09-03 08:45:23</t>
   </si>
   <si>
     <t>API-TC-125</t>
@@ -2143,7 +2143,7 @@
     <t>Add remote ICE candidate to peer connection [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:37:59</t>
+    <t>2026-09-03 08:45:34</t>
   </si>
   <si>
     <t>API-TC-126</t>
@@ -2152,7 +2152,7 @@
     <t>Toggle local audio track enabled state (Mute/Unmute) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:10</t>
+    <t>2026-09-03 08:45:45</t>
   </si>
   <si>
     <t>API-TC-127</t>
@@ -2161,7 +2161,7 @@
     <t>Toggle local video track enabled state (Video on/off) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:21</t>
+    <t>2026-09-03 08:45:56</t>
   </si>
   <si>
     <t>API-TC-128</t>
@@ -2170,7 +2170,7 @@
     <t>Screen share getDisplayMedia stream track replacement [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:32</t>
+    <t>2026-09-03 08:46:07</t>
   </si>
   <si>
     <t>API-TC-129</t>
@@ -2179,7 +2179,7 @@
     <t>Handle ICE connection state transitions (connected/disconnected) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:43</t>
+    <t>2026-09-03 08:46:18</t>
   </si>
   <si>
     <t>API-TC-130</t>
@@ -2188,7 +2188,7 @@
     <t>Clean teardown and close of WebRTC peer connection [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:38:54</t>
+    <t>2026-09-03 08:46:29</t>
   </si>
   <si>
     <t>API-TC-131</t>
@@ -2197,7 +2197,7 @@
     <t>Calculate mutual skill compatibility score (0-100%) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:05</t>
+    <t>2026-09-03 08:46:40</t>
   </si>
   <si>
     <t>API-TC-132</t>
@@ -2206,7 +2206,7 @@
     <t>Rank match recommendations by rating and compatibility [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:16</t>
+    <t>2026-09-03 08:46:51</t>
   </si>
   <si>
     <t>API-TC-133</t>
@@ -2215,7 +2215,7 @@
     <t>Filter out blocked users from match recommendations [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:27</t>
+    <t>2026-09-03 08:47:02</t>
   </si>
   <si>
     <t>API-TC-134</t>
@@ -2224,7 +2224,7 @@
     <t>Boost online and responsive mentors in search ranking [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:38</t>
+    <t>2026-09-03 08:47:13</t>
   </si>
   <si>
     <t>API-TC-135</t>
@@ -2233,7 +2233,7 @@
     <t>Skill taxonomy category mapper and synonym resolver [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:39:49</t>
+    <t>2026-09-03 08:47:24</t>
   </si>
   <si>
     <t>API-TC-136</t>
@@ -2242,7 +2242,7 @@
     <t>Complementary skill pair suggestion engine [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:00</t>
+    <t>2026-09-03 08:47:35</t>
   </si>
   <si>
     <t>API-TC-137</t>
@@ -2251,7 +2251,7 @@
     <t>Calculate user mentor tier and badge eligibility [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:11</t>
+    <t>2026-09-03 08:47:46</t>
   </si>
   <si>
     <t>API-TC-138</t>
@@ -2260,7 +2260,7 @@
     <t>Timezone difference calculator for mutual availability [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:22</t>
+    <t>2026-09-03 08:47:57</t>
   </si>
   <si>
     <t>API-TC-139</t>
@@ -2269,7 +2269,7 @@
     <t>Skill swap credit balance ledger calculation [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:33</t>
+    <t>2026-09-03 08:48:08</t>
   </si>
   <si>
     <t>API-TC-140</t>
@@ -2278,7 +2278,7 @@
     <t>Check credit balance sufficiency before booking request [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:44</t>
+    <t>2026-09-03 08:48:19</t>
   </si>
   <si>
     <t>API-TC-141</t>
@@ -2287,7 +2287,7 @@
     <t>Generate 30-minute booking slots from working hours [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:40:55</t>
+    <t>2026-09-03 08:48:30</t>
   </si>
   <si>
     <t>API-TC-142</t>
@@ -2296,7 +2296,7 @@
     <t>Conflict detector flags overlapping session bookings [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:06</t>
+    <t>2026-09-03 08:48:41</t>
   </si>
   <si>
     <t>API-TC-143</t>
@@ -2305,7 +2305,7 @@
     <t>Format ISO date string to localized readable format [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:17</t>
+    <t>2026-09-03 08:48:52</t>
   </si>
   <si>
     <t>API-TC-144</t>
@@ -2314,7 +2314,7 @@
     <t>Time slot conversion across different timezones [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:28</t>
+    <t>2026-09-03 08:49:03</t>
   </si>
   <si>
     <t>API-TC-145</t>
@@ -2323,7 +2323,7 @@
     <t>Recurring weekly availability mask generator [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:39</t>
+    <t>2026-09-03 08:49:14</t>
   </si>
   <si>
     <t>API-TC-146</t>
@@ -2332,7 +2332,7 @@
     <t>Generate iCalendar (.ics) format file string [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:41:50</t>
+    <t>2026-09-03 08:49:25</t>
   </si>
   <si>
     <t>API-TC-147</t>
@@ -2341,7 +2341,7 @@
     <t>Session countdown duration calculator (days/hours/minutes) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:01</t>
+    <t>2026-09-03 08:49:36</t>
   </si>
   <si>
     <t>API-TC-148</t>
@@ -2350,7 +2350,7 @@
     <t>Calculate session duration in minutes from start and end [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:12</t>
+    <t>2026-09-03 08:49:47</t>
   </si>
   <si>
     <t>API-TC-149</t>
@@ -2359,7 +2359,7 @@
     <t>Enforce minimum cancellation notice period (e.g. 2 hours) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:23</t>
+    <t>2026-09-03 08:49:58</t>
   </si>
   <si>
     <t>API-TC-150</t>
@@ -2368,7 +2368,7 @@
     <t>Calculate buffer time between consecutive bookings [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:34</t>
+    <t>2026-09-03 08:50:09</t>
   </si>
   <si>
     <t>API-TC-151</t>
@@ -2377,7 +2377,7 @@
     <t>Sanitize user profile payload before writing to database [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:45</t>
+    <t>2026-09-03 08:50:20</t>
   </si>
   <si>
     <t>API-TC-152</t>
@@ -2386,7 +2386,7 @@
     <t>Format user initials for avatar fallback display [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:42:56</t>
+    <t>2026-09-03 08:50:31</t>
   </si>
   <si>
     <t>API-TC-153</t>
@@ -2395,7 +2395,7 @@
     <t>Truncate text snippet with ellipsis at word boundary [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:07</t>
+    <t>2026-09-03 08:50:42</t>
   </si>
   <si>
     <t>API-TC-154</t>
@@ -2404,7 +2404,7 @@
     <t>Parse search query tokens into normalized search array [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:18</t>
+    <t>2026-09-03 08:50:53</t>
   </si>
   <si>
     <t>API-TC-155</t>
@@ -2413,7 +2413,7 @@
     <t>Format star rating to 1 decimal place with round [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:29</t>
+    <t>2026-09-03 08:51:04</t>
   </si>
   <si>
     <t>API-TC-156</t>
@@ -2422,7 +2422,7 @@
     <t>Generate unique room ID for WebRTC video session [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:40</t>
+    <t>2026-09-03 08:51:15</t>
   </si>
   <si>
     <t>API-TC-157</t>
@@ -2431,7 +2431,7 @@
     <t>Deep clone nested state object immutably [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:43:51</t>
+    <t>2026-09-03 08:51:26</t>
   </si>
   <si>
     <t>API-TC-158</t>
@@ -2440,7 +2440,7 @@
     <t>Debounce function wrapper delays execution until rest period [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:02</t>
+    <t>2026-09-03 08:51:37</t>
   </si>
   <si>
     <t>API-TC-159</t>
@@ -2449,7 +2449,7 @@
     <t>Throttle function limits execution rate to fixed interval [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:13</t>
+    <t>2026-09-03 08:51:48</t>
   </si>
   <si>
     <t>API-TC-160</t>
@@ -2458,7 +2458,7 @@
     <t>Format file size in bytes to human readable (KB, MB) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:24</t>
+    <t>2026-09-03 08:51:59</t>
   </si>
   <si>
     <t>API-TC-161</t>
@@ -2467,7 +2467,7 @@
     <t>Format swap request notification payload [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:35</t>
+    <t>2026-09-03 08:52:10</t>
   </si>
   <si>
     <t>API-TC-162</t>
@@ -2476,7 +2476,7 @@
     <t>Filter unread notifications count query [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:46</t>
+    <t>2026-09-03 08:52:21</t>
   </si>
   <si>
     <t>API-TC-163</t>
@@ -2485,7 +2485,7 @@
     <t>Batch mark all notifications as read [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:44:57</t>
+    <t>2026-09-03 08:52:32</t>
   </si>
   <si>
     <t>API-TC-164</t>
@@ -2494,7 +2494,7 @@
     <t>Rate limiter prevents spamming notification requests [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:08</t>
+    <t>2026-09-03 08:52:43</t>
   </si>
   <si>
     <t>API-TC-165</t>
@@ -2503,7 +2503,7 @@
     <t>In-app toast alert message queue manager [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:19</t>
+    <t>2026-09-03 08:52:54</t>
   </si>
   <si>
     <t>API-TC-166</t>
@@ -2512,7 +2512,7 @@
     <t>Group chat messages by date timestamp headers [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:30</t>
+    <t>2026-09-03 08:53:05</t>
   </si>
   <si>
     <t>API-TC-167</t>
@@ -2521,7 +2521,7 @@
     <t>Sound effect player trigger for incoming call chime [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:41</t>
+    <t>2026-09-03 08:53:16</t>
   </si>
   <si>
     <t>API-TC-168</t>
@@ -2530,7 +2530,7 @@
     <t>Badge counter calculation for active sidebar tabs [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:45:52</t>
+    <t>2026-09-03 08:53:27</t>
   </si>
   <si>
     <t>API-TC-169</t>
@@ -2539,7 +2539,7 @@
     <t>Dispatch custom browser DOM event for global state sync [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:03</t>
+    <t>2026-09-03 08:53:38</t>
   </si>
   <si>
     <t>API-TC-170</t>
@@ -2548,7 +2548,7 @@
     <t>Format system announcement notification banner [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:14</t>
+    <t>2026-09-03 08:53:49</t>
   </si>
   <si>
     <t>API-TC-171</t>
@@ -2557,7 +2557,7 @@
     <t>Calculate average rating from array of review scores [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:25</t>
+    <t>2026-09-03 08:54:00</t>
   </si>
   <si>
     <t>API-TC-172</t>
@@ -2566,7 +2566,7 @@
     <t>Calculate rating distribution breakdown (1-star to 5-star %) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:36</t>
+    <t>2026-09-03 08:54:11</t>
   </si>
   <si>
     <t>API-TC-173</t>
@@ -2575,7 +2575,7 @@
     <t>Validate review submission minimum word count and rating [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:47</t>
+    <t>2026-09-03 08:54:22</t>
   </si>
   <si>
     <t>API-TC-174</t>
@@ -2584,7 +2584,7 @@
     <t>Prevent duplicate review submission for same session [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:46:58</t>
+    <t>2026-09-03 08:54:33</t>
   </si>
   <si>
     <t>API-TC-175</t>
@@ -2593,7 +2593,7 @@
     <t>Calculate mentor level badge progression points [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:09</t>
+    <t>2026-09-03 08:54:44</t>
   </si>
   <si>
     <t>API-TC-176</t>
@@ -2602,7 +2602,7 @@
     <t>Filter and sanitize inappropriate words from review comment [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:20</t>
+    <t>2026-09-03 08:54:55</t>
   </si>
   <si>
     <t>API-TC-177</t>
@@ -2611,7 +2611,7 @@
     <t>Helpful review vote counter increment (+1 helpful) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:31</t>
+    <t>2026-09-03 08:55:06</t>
   </si>
   <si>
     <t>API-TC-178</t>
@@ -2620,7 +2620,7 @@
     <t>Calculate response rate percentage (e.g. 96%) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:42</t>
+    <t>2026-09-03 08:55:17</t>
   </si>
   <si>
     <t>API-TC-179</t>
@@ -2629,7 +2629,7 @@
     <t>Calculate average response time in hours/minutes [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:47:53</t>
+    <t>2026-09-03 08:55:28</t>
   </si>
   <si>
     <t>API-TC-180</t>
@@ -2638,7 +2638,7 @@
     <t>Verify swap completion before allowing review submission [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:04</t>
+    <t>2026-09-03 08:55:39</t>
   </si>
   <si>
     <t>API-TC-181</t>
@@ -2647,7 +2647,7 @@
     <t>Network timeout retry handler with exponential backoff [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:15</t>
+    <t>2026-09-03 08:55:50</t>
   </si>
   <si>
     <t>API-TC-182</t>
@@ -2656,7 +2656,7 @@
     <t>Graceful fallback to mock data when Firebase offline [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:26</t>
+    <t>2026-09-03 08:56:01</t>
   </si>
   <si>
     <t>API-TC-183</t>
@@ -2665,7 +2665,7 @@
     <t>Parse and format unexpected runtime errors cleanly [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:37</t>
+    <t>2026-09-03 08:56:12</t>
   </si>
   <si>
     <t>API-TC-184</t>
@@ -2674,7 +2674,7 @@
     <t>Local storage quota exceeded fallback strategy [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:48</t>
+    <t>2026-09-03 08:56:23</t>
   </si>
   <si>
     <t>API-TC-185</t>
@@ -2683,7 +2683,7 @@
     <t>Invalid JSON payload decoder safe parser [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:48:59</t>
+    <t>2026-09-03 08:56:34</t>
   </si>
   <si>
     <t>API-TC-186</t>
@@ -2692,7 +2692,7 @@
     <t>WebRTC device permission denied recovery guide [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:10</t>
+    <t>2026-09-03 08:56:45</t>
   </si>
   <si>
     <t>API-TC-187</t>
@@ -2701,7 +2701,7 @@
     <t>Session token expiration auto-refresh interceptor [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:21</t>
+    <t>2026-09-03 08:56:56</t>
   </si>
   <si>
     <t>API-TC-188</t>
@@ -2710,7 +2710,7 @@
     <t>Handle concurrent edit collision on user profile document [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:32</t>
+    <t>2026-09-03 08:57:07</t>
   </si>
   <si>
     <t>API-TC-189</t>
@@ -2719,7 +2719,7 @@
     <t>File upload size validator (reject files &gt; 10MB) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:43</t>
+    <t>2026-09-03 08:57:18</t>
   </si>
   <si>
     <t>API-TC-190</t>
@@ -2728,7 +2728,7 @@
     <t>File upload MIME type validator (images &amp; pdf only) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:49:54</t>
+    <t>2026-09-03 08:57:29</t>
   </si>
   <si>
     <t>API-TC-191</t>
@@ -2737,7 +2737,7 @@
     <t>Generate secure cryptographically random session token [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:05</t>
+    <t>2026-09-03 08:57:40</t>
   </si>
   <si>
     <t>API-TC-192</t>
@@ -2746,7 +2746,7 @@
     <t>Hash sensitive strings with SHA-256 algorithm [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:16</t>
+    <t>2026-09-03 08:57:51</t>
   </si>
   <si>
     <t>API-TC-193</t>
@@ -2755,7 +2755,7 @@
     <t>Validate JWT expiration timestamp is in future [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:27</t>
+    <t>2026-09-03 08:58:02</t>
   </si>
   <si>
     <t>API-TC-194</t>
@@ -2764,7 +2764,7 @@
     <t>Check user role permissions (Admin, Moderator, Member) [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:38</t>
+    <t>2026-09-03 08:58:13</t>
   </si>
   <si>
     <t>API-TC-195</t>
@@ -2773,7 +2773,7 @@
     <t>Prevent cross-user private message access [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:50:49</t>
+    <t>2026-09-03 08:58:24</t>
   </si>
   <si>
     <t>API-TC-196</t>
@@ -2782,7 +2782,7 @@
     <t>Prevent unauthorized calendar booking modification [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:00</t>
+    <t>2026-09-03 08:58:35</t>
   </si>
   <si>
     <t>API-TC-197</t>
@@ -2791,7 +2791,7 @@
     <t>Sanitize HTML tags from user inputs to prevent XSS [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:11</t>
+    <t>2026-09-03 08:58:46</t>
   </si>
   <si>
     <t>API-TC-198</t>
@@ -2800,7 +2800,7 @@
     <t>Validate CSRF anti-forgery token in stateful requests [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:22</t>
+    <t>2026-09-03 08:58:57</t>
   </si>
   <si>
     <t>API-TC-199</t>
@@ -2809,7 +2809,7 @@
     <t>Check password hash comparison timing safe equal [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:33</t>
+    <t>2026-09-03 08:59:08</t>
   </si>
   <si>
     <t>API-TC-200</t>
@@ -2818,7 +2818,7 @@
     <t>Verify user email verification flag before restricted actions [Mocked Async Resolution]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:44</t>
+    <t>2026-09-03 08:59:19</t>
   </si>
   <si>
     <t>API-TC-201</t>
@@ -2827,7 +2827,7 @@
     <t>signUpWithEmailAndPassword returns user credential with uid [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:51:55</t>
+    <t>2026-09-03 08:59:30</t>
   </si>
   <si>
     <t>API-TC-202</t>
@@ -2836,7 +2836,7 @@
     <t>signInWithEmailAndPassword validates credentials and sets session [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:06</t>
+    <t>2026-09-03 08:59:41</t>
   </si>
   <si>
     <t>API-TC-203</t>
@@ -2845,7 +2845,7 @@
     <t>signOut cleans up local session state and listeners [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:17</t>
+    <t>2026-09-03 08:59:52</t>
   </si>
   <si>
     <t>API-TC-204</t>
@@ -2854,7 +2854,7 @@
     <t>sendPasswordResetEmail formats Firebase reset request [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:28</t>
+    <t>2026-09-03 09:00:03</t>
   </si>
   <si>
     <t>API-TC-205</t>
@@ -2863,7 +2863,7 @@
     <t>onAuthStateChanged event emitter subscriber handling [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:39</t>
+    <t>2026-09-03 09:00:14</t>
   </si>
   <si>
     <t>API-TC-206</t>
@@ -2872,7 +2872,7 @@
     <t>JWT token ID token retrieval with forceRefresh parameter [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:52:50</t>
+    <t>2026-09-03 09:00:25</t>
   </si>
   <si>
     <t>API-TC-207</t>
@@ -2881,7 +2881,7 @@
     <t>GoogleAuthProvider credential parsing and account linking [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:01</t>
+    <t>2026-09-03 09:00:36</t>
   </si>
   <si>
     <t>API-TC-208</t>
@@ -2890,7 +2890,7 @@
     <t>Auth error code mapping (auth/user-not-found to human message) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:12</t>
+    <t>2026-09-03 09:00:47</t>
   </si>
   <si>
     <t>API-TC-209</t>
@@ -2899,7 +2899,7 @@
     <t>Auth error code mapping (auth/wrong-password) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:23</t>
+    <t>2026-09-03 09:00:58</t>
   </si>
   <si>
     <t>API-TC-210</t>
@@ -2908,7 +2908,7 @@
     <t>Update user display name and photoURL in Firebase Auth [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:34</t>
+    <t>2026-09-03 09:01:09</t>
   </si>
   <si>
     <t>API-TC-211</t>
@@ -2917,7 +2917,7 @@
     <t>createUserProfile creates document in users collection [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:45</t>
+    <t>2026-09-03 09:01:20</t>
   </si>
   <si>
     <t>API-TC-212</t>
@@ -2926,7 +2926,7 @@
     <t>getUserProfile fetches user document by ID [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:53:56</t>
+    <t>2026-09-03 09:01:31</t>
   </si>
   <si>
     <t>API-TC-213</t>
@@ -2935,7 +2935,7 @@
     <t>updateUserProfile performs partial merge update [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:07</t>
+    <t>2026-09-03 09:01:42</t>
   </si>
   <si>
     <t>API-TC-214</t>
@@ -2944,7 +2944,7 @@
     <t>searchUsersBySkill query builder with array-contains [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:18</t>
+    <t>2026-09-03 09:01:53</t>
   </si>
   <si>
     <t>API-TC-215</t>
@@ -2953,7 +2953,7 @@
     <t>searchUsersWithFilters composite query with category and level [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:29</t>
+    <t>2026-09-03 09:02:04</t>
   </si>
   <si>
     <t>API-TC-216</t>
@@ -2962,7 +2962,7 @@
     <t>createSwapRequest creates request document with Pending status [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:40</t>
+    <t>2026-09-03 09:02:15</t>
   </si>
   <si>
     <t>API-TC-217</t>
@@ -2971,7 +2971,7 @@
     <t>respondToSwapRequest updates status to Accepted/Declined [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:54:51</t>
+    <t>2026-09-03 09:02:26</t>
   </si>
   <si>
     <t>API-TC-218</t>
@@ -2980,7 +2980,7 @@
     <t>subscribeToConversations listens to user message channels [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:02</t>
+    <t>2026-09-03 09:02:37</t>
   </si>
   <si>
     <t>API-TC-219</t>
@@ -2989,7 +2989,7 @@
     <t>sendMessage writes to messages subcollection with serverTimestamp [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:13</t>
+    <t>2026-09-03 09:02:48</t>
   </si>
   <si>
     <t>API-TC-220</t>
@@ -2998,7 +2998,7 @@
     <t>markMessageAsRead updates readBy array in message doc [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:24</t>
+    <t>2026-09-03 09:02:59</t>
   </si>
   <si>
     <t>API-TC-221</t>
@@ -3007,7 +3007,7 @@
     <t>Create RTCPeerConnection with STUN/TURN server configuration [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:35</t>
+    <t>2026-09-03 09:03:10</t>
   </si>
   <si>
     <t>API-TC-222</t>
@@ -3016,7 +3016,7 @@
     <t>Create WebRTC Offer and set local description [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:46</t>
+    <t>2026-09-03 09:03:21</t>
   </si>
   <si>
     <t>API-TC-223</t>
@@ -3025,7 +3025,7 @@
     <t>Create WebRTC Answer to remote offer [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:55:57</t>
+    <t>2026-09-03 09:03:32</t>
   </si>
   <si>
     <t>API-TC-224</t>
@@ -3034,7 +3034,7 @@
     <t>ICE candidate gathering and Firestore signaling exchange [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:08</t>
+    <t>2026-09-03 09:03:43</t>
   </si>
   <si>
     <t>API-TC-225</t>
@@ -3043,7 +3043,7 @@
     <t>Add remote ICE candidate to peer connection [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:19</t>
+    <t>2026-09-03 09:03:54</t>
   </si>
   <si>
     <t>API-TC-226</t>
@@ -3052,7 +3052,7 @@
     <t>Toggle local audio track enabled state (Mute/Unmute) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:30</t>
+    <t>2026-09-03 09:04:05</t>
   </si>
   <si>
     <t>API-TC-227</t>
@@ -3061,7 +3061,7 @@
     <t>Toggle local video track enabled state (Video on/off) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:41</t>
+    <t>2026-09-03 09:04:16</t>
   </si>
   <si>
     <t>API-TC-228</t>
@@ -3070,7 +3070,7 @@
     <t>Screen share getDisplayMedia stream track replacement [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:56:52</t>
+    <t>2026-09-03 09:04:27</t>
   </si>
   <si>
     <t>API-TC-229</t>
@@ -3079,7 +3079,7 @@
     <t>Handle ICE connection state transitions (connected/disconnected) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:03</t>
+    <t>2026-09-03 09:04:38</t>
   </si>
   <si>
     <t>API-TC-230</t>
@@ -3088,7 +3088,7 @@
     <t>Clean teardown and close of WebRTC peer connection [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:14</t>
+    <t>2026-09-03 09:04:49</t>
   </si>
   <si>
     <t>API-TC-231</t>
@@ -3097,7 +3097,7 @@
     <t>Calculate mutual skill compatibility score (0-100%) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:25</t>
+    <t>2026-09-03 09:05:00</t>
   </si>
   <si>
     <t>API-TC-232</t>
@@ -3106,7 +3106,7 @@
     <t>Rank match recommendations by rating and compatibility [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:36</t>
+    <t>2026-09-03 09:05:11</t>
   </si>
   <si>
     <t>API-TC-233</t>
@@ -3115,7 +3115,7 @@
     <t>Filter out blocked users from match recommendations [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:47</t>
+    <t>2026-09-03 09:05:22</t>
   </si>
   <si>
     <t>API-TC-234</t>
@@ -3124,7 +3124,7 @@
     <t>Boost online and responsive mentors in search ranking [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:57:58</t>
+    <t>2026-09-03 09:05:33</t>
   </si>
   <si>
     <t>API-TC-235</t>
@@ -3133,7 +3133,7 @@
     <t>Skill taxonomy category mapper and synonym resolver [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:09</t>
+    <t>2026-09-03 09:05:44</t>
   </si>
   <si>
     <t>API-TC-236</t>
@@ -3142,7 +3142,7 @@
     <t>Complementary skill pair suggestion engine [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:20</t>
+    <t>2026-09-03 09:05:55</t>
   </si>
   <si>
     <t>API-TC-237</t>
@@ -3151,7 +3151,7 @@
     <t>Calculate user mentor tier and badge eligibility [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:31</t>
+    <t>2026-09-03 09:06:06</t>
   </si>
   <si>
     <t>API-TC-238</t>
@@ -3160,7 +3160,7 @@
     <t>Timezone difference calculator for mutual availability [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:42</t>
+    <t>2026-09-03 09:06:17</t>
   </si>
   <si>
     <t>API-TC-239</t>
@@ -3169,7 +3169,7 @@
     <t>Skill swap credit balance ledger calculation [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:58:53</t>
+    <t>2026-09-03 09:06:28</t>
   </si>
   <si>
     <t>API-TC-240</t>
@@ -3178,7 +3178,7 @@
     <t>Check credit balance sufficiency before booking request [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:04</t>
+    <t>2026-09-03 09:06:39</t>
   </si>
   <si>
     <t>API-TC-241</t>
@@ -3187,7 +3187,7 @@
     <t>Generate 30-minute booking slots from working hours [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:15</t>
+    <t>2026-09-03 09:06:50</t>
   </si>
   <si>
     <t>API-TC-242</t>
@@ -3196,7 +3196,7 @@
     <t>Conflict detector flags overlapping session bookings [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:26</t>
+    <t>2026-09-03 09:07:01</t>
   </si>
   <si>
     <t>API-TC-243</t>
@@ -3205,7 +3205,7 @@
     <t>Format ISO date string to localized readable format [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:37</t>
+    <t>2026-09-03 09:07:12</t>
   </si>
   <si>
     <t>API-TC-244</t>
@@ -3214,7 +3214,7 @@
     <t>Time slot conversion across different timezones [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:48</t>
+    <t>2026-09-03 09:07:23</t>
   </si>
   <si>
     <t>API-TC-245</t>
@@ -3223,7 +3223,7 @@
     <t>Recurring weekly availability mask generator [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 08:59:59</t>
+    <t>2026-09-03 09:07:34</t>
   </si>
   <si>
     <t>API-TC-246</t>
@@ -3232,7 +3232,7 @@
     <t>Generate iCalendar (.ics) format file string [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:10</t>
+    <t>2026-09-03 09:07:45</t>
   </si>
   <si>
     <t>API-TC-247</t>
@@ -3241,7 +3241,7 @@
     <t>Session countdown duration calculator (days/hours/minutes) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:21</t>
+    <t>2026-09-03 09:07:56</t>
   </si>
   <si>
     <t>API-TC-248</t>
@@ -3250,7 +3250,7 @@
     <t>Calculate session duration in minutes from start and end [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:32</t>
+    <t>2026-09-03 09:08:07</t>
   </si>
   <si>
     <t>API-TC-249</t>
@@ -3259,7 +3259,7 @@
     <t>Enforce minimum cancellation notice period (e.g. 2 hours) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:43</t>
+    <t>2026-09-03 09:08:18</t>
   </si>
   <si>
     <t>API-TC-250</t>
@@ -3268,7 +3268,7 @@
     <t>Calculate buffer time between consecutive bookings [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:00:54</t>
+    <t>2026-09-03 09:08:29</t>
   </si>
   <si>
     <t>API-TC-251</t>
@@ -3277,7 +3277,7 @@
     <t>Sanitize user profile payload before writing to database [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:05</t>
+    <t>2026-09-03 09:08:40</t>
   </si>
   <si>
     <t>API-TC-252</t>
@@ -3286,7 +3286,7 @@
     <t>Format user initials for avatar fallback display [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:16</t>
+    <t>2026-09-03 09:08:51</t>
   </si>
   <si>
     <t>API-TC-253</t>
@@ -3295,7 +3295,7 @@
     <t>Truncate text snippet with ellipsis at word boundary [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:27</t>
+    <t>2026-09-03 09:09:02</t>
   </si>
   <si>
     <t>API-TC-254</t>
@@ -3304,7 +3304,7 @@
     <t>Parse search query tokens into normalized search array [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:38</t>
+    <t>2026-09-03 09:09:13</t>
   </si>
   <si>
     <t>API-TC-255</t>
@@ -3313,7 +3313,7 @@
     <t>Format star rating to 1 decimal place with round [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:01:49</t>
+    <t>2026-09-03 09:09:24</t>
   </si>
   <si>
     <t>API-TC-256</t>
@@ -3322,7 +3322,7 @@
     <t>Generate unique room ID for WebRTC video session [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:00</t>
+    <t>2026-09-03 09:09:35</t>
   </si>
   <si>
     <t>API-TC-257</t>
@@ -3331,7 +3331,7 @@
     <t>Deep clone nested state object immutably [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:11</t>
+    <t>2026-09-03 09:09:46</t>
   </si>
   <si>
     <t>API-TC-258</t>
@@ -3340,7 +3340,7 @@
     <t>Debounce function wrapper delays execution until rest period [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:22</t>
+    <t>2026-09-03 09:09:57</t>
   </si>
   <si>
     <t>API-TC-259</t>
@@ -3349,7 +3349,7 @@
     <t>Throttle function limits execution rate to fixed interval [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:33</t>
+    <t>2026-09-03 09:10:08</t>
   </si>
   <si>
     <t>API-TC-260</t>
@@ -3358,7 +3358,7 @@
     <t>Format file size in bytes to human readable (KB, MB) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:44</t>
+    <t>2026-09-03 09:10:19</t>
   </si>
   <si>
     <t>API-TC-261</t>
@@ -3367,7 +3367,7 @@
     <t>Format swap request notification payload [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:02:55</t>
+    <t>2026-09-03 09:10:30</t>
   </si>
   <si>
     <t>API-TC-262</t>
@@ -3376,7 +3376,7 @@
     <t>Filter unread notifications count query [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:06</t>
+    <t>2026-09-03 09:10:41</t>
   </si>
   <si>
     <t>API-TC-263</t>
@@ -3385,7 +3385,7 @@
     <t>Batch mark all notifications as read [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:17</t>
+    <t>2026-09-03 09:10:52</t>
   </si>
   <si>
     <t>API-TC-264</t>
@@ -3394,7 +3394,7 @@
     <t>Rate limiter prevents spamming notification requests [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:28</t>
+    <t>2026-09-03 09:11:03</t>
   </si>
   <si>
     <t>API-TC-265</t>
@@ -3403,7 +3403,7 @@
     <t>In-app toast alert message queue manager [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:39</t>
+    <t>2026-09-03 09:11:14</t>
   </si>
   <si>
     <t>API-TC-266</t>
@@ -3412,7 +3412,7 @@
     <t>Group chat messages by date timestamp headers [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:03:50</t>
+    <t>2026-09-03 09:11:25</t>
   </si>
   <si>
     <t>API-TC-267</t>
@@ -3421,7 +3421,7 @@
     <t>Sound effect player trigger for incoming call chime [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:01</t>
+    <t>2026-09-03 09:11:36</t>
   </si>
   <si>
     <t>API-TC-268</t>
@@ -3430,7 +3430,7 @@
     <t>Badge counter calculation for active sidebar tabs [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:12</t>
+    <t>2026-09-03 09:11:47</t>
   </si>
   <si>
     <t>API-TC-269</t>
@@ -3439,7 +3439,7 @@
     <t>Dispatch custom browser DOM event for global state sync [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:23</t>
+    <t>2026-09-03 09:11:58</t>
   </si>
   <si>
     <t>API-TC-270</t>
@@ -3448,7 +3448,7 @@
     <t>Format system announcement notification banner [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:34</t>
+    <t>2026-09-03 09:12:09</t>
   </si>
   <si>
     <t>API-TC-271</t>
@@ -3457,7 +3457,7 @@
     <t>Calculate average rating from array of review scores [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:45</t>
+    <t>2026-09-03 09:12:20</t>
   </si>
   <si>
     <t>API-TC-272</t>
@@ -3466,7 +3466,7 @@
     <t>Calculate rating distribution breakdown (1-star to 5-star %) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:04:56</t>
+    <t>2026-09-03 09:12:31</t>
   </si>
   <si>
     <t>API-TC-273</t>
@@ -3475,7 +3475,7 @@
     <t>Validate review submission minimum word count and rating [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:07</t>
+    <t>2026-09-03 09:12:42</t>
   </si>
   <si>
     <t>API-TC-274</t>
@@ -3484,7 +3484,7 @@
     <t>Prevent duplicate review submission for same session [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:18</t>
+    <t>2026-09-03 09:12:53</t>
   </si>
   <si>
     <t>API-TC-275</t>
@@ -3493,7 +3493,7 @@
     <t>Calculate mentor level badge progression points [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:29</t>
+    <t>2026-09-03 09:13:04</t>
   </si>
   <si>
     <t>API-TC-276</t>
@@ -3502,7 +3502,7 @@
     <t>Filter and sanitize inappropriate words from review comment [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:40</t>
+    <t>2026-09-03 09:13:15</t>
   </si>
   <si>
     <t>API-TC-277</t>
@@ -3511,7 +3511,7 @@
     <t>Helpful review vote counter increment (+1 helpful) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:05:51</t>
+    <t>2026-09-03 09:13:26</t>
   </si>
   <si>
     <t>API-TC-278</t>
@@ -3520,7 +3520,7 @@
     <t>Calculate response rate percentage (e.g. 96%) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:02</t>
+    <t>2026-09-03 09:13:37</t>
   </si>
   <si>
     <t>API-TC-279</t>
@@ -3529,7 +3529,7 @@
     <t>Calculate average response time in hours/minutes [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:13</t>
+    <t>2026-09-03 09:13:48</t>
   </si>
   <si>
     <t>API-TC-280</t>
@@ -3538,7 +3538,7 @@
     <t>Verify swap completion before allowing review submission [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:24</t>
+    <t>2026-09-03 09:13:59</t>
   </si>
   <si>
     <t>API-TC-281</t>
@@ -3547,7 +3547,7 @@
     <t>Network timeout retry handler with exponential backoff [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:35</t>
+    <t>2026-09-03 09:14:10</t>
   </si>
   <si>
     <t>API-TC-282</t>
@@ -3556,7 +3556,7 @@
     <t>Graceful fallback to mock data when Firebase offline [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:46</t>
+    <t>2026-09-03 09:14:21</t>
   </si>
   <si>
     <t>API-TC-283</t>
@@ -3565,7 +3565,7 @@
     <t>Parse and format unexpected runtime errors cleanly [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:06:57</t>
+    <t>2026-09-03 09:14:32</t>
   </si>
   <si>
     <t>API-TC-284</t>
@@ -3574,7 +3574,7 @@
     <t>Local storage quota exceeded fallback strategy [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:08</t>
+    <t>2026-09-03 09:14:43</t>
   </si>
   <si>
     <t>API-TC-285</t>
@@ -3583,7 +3583,7 @@
     <t>Invalid JSON payload decoder safe parser [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:19</t>
+    <t>2026-09-03 09:14:54</t>
   </si>
   <si>
     <t>API-TC-286</t>
@@ -3592,7 +3592,7 @@
     <t>WebRTC device permission denied recovery guide [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:30</t>
+    <t>2026-09-03 09:15:05</t>
   </si>
   <si>
     <t>API-TC-287</t>
@@ -3601,7 +3601,7 @@
     <t>Session token expiration auto-refresh interceptor [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:41</t>
+    <t>2026-09-03 09:15:16</t>
   </si>
   <si>
     <t>API-TC-288</t>
@@ -3610,7 +3610,7 @@
     <t>Handle concurrent edit collision on user profile document [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:07:52</t>
+    <t>2026-09-03 09:15:27</t>
   </si>
   <si>
     <t>API-TC-289</t>
@@ -3619,7 +3619,7 @@
     <t>File upload size validator (reject files &gt; 10MB) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:03</t>
+    <t>2026-09-03 09:15:38</t>
   </si>
   <si>
     <t>API-TC-290</t>
@@ -3628,7 +3628,7 @@
     <t>File upload MIME type validator (images &amp; pdf only) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:14</t>
+    <t>2026-09-03 09:15:49</t>
   </si>
   <si>
     <t>API-TC-291</t>
@@ -3637,7 +3637,7 @@
     <t>Generate secure cryptographically random session token [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:25</t>
+    <t>2026-09-03 09:16:00</t>
   </si>
   <si>
     <t>API-TC-292</t>
@@ -3646,7 +3646,7 @@
     <t>Hash sensitive strings with SHA-256 algorithm [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:36</t>
+    <t>2026-09-03 09:16:11</t>
   </si>
   <si>
     <t>API-TC-293</t>
@@ -3655,7 +3655,7 @@
     <t>Validate JWT expiration timestamp is in future [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:47</t>
+    <t>2026-09-03 09:16:22</t>
   </si>
   <si>
     <t>API-TC-294</t>
@@ -3664,7 +3664,7 @@
     <t>Check user role permissions (Admin, Moderator, Member) [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:08:58</t>
+    <t>2026-09-03 09:16:33</t>
   </si>
   <si>
     <t>API-TC-295</t>
@@ -3673,7 +3673,7 @@
     <t>Prevent cross-user private message access [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:09</t>
+    <t>2026-09-03 09:16:44</t>
   </si>
   <si>
     <t>API-TC-296</t>
@@ -3682,7 +3682,7 @@
     <t>Prevent unauthorized calendar booking modification [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:20</t>
+    <t>2026-09-03 09:16:55</t>
   </si>
   <si>
     <t>API-TC-297</t>
@@ -3691,7 +3691,7 @@
     <t>Sanitize HTML tags from user inputs to prevent XSS [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:31</t>
+    <t>2026-09-03 09:17:06</t>
   </si>
   <si>
     <t>API-TC-298</t>
@@ -3700,7 +3700,7 @@
     <t>Validate CSRF anti-forgery token in stateful requests [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:42</t>
+    <t>2026-09-03 09:17:17</t>
   </si>
   <si>
     <t>API-TC-299</t>
@@ -3709,7 +3709,7 @@
     <t>Check password hash comparison timing safe equal [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:09:53</t>
+    <t>2026-09-03 09:17:28</t>
   </si>
   <si>
     <t>API-TC-300</t>
@@ -3718,7 +3718,7 @@
     <t>Verify user email verification flag before restricted actions [Boundary &amp; Invalidation Check]</t>
   </si>
   <si>
-    <t>2026-09-03 09:10:04</t>
+    <t>2026-09-03 09:17:39</t>
   </si>
 </sst>
 </file>
@@ -4260,7 +4260,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -4301,7 +4301,7 @@
         <v>29</v>
       </c>
       <c r="J3" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>22</v>
@@ -4342,7 +4342,7 @@
         <v>36</v>
       </c>
       <c r="J4" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>22</v>
@@ -4424,7 +4424,7 @@
         <v>49</v>
       </c>
       <c r="J6" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>22</v>
@@ -4465,7 +4465,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="5">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>22</v>
@@ -4506,7 +4506,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>22</v>
@@ -4547,7 +4547,7 @@
         <v>67</v>
       </c>
       <c r="J9" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>22</v>
@@ -4588,7 +4588,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>22</v>
@@ -4629,7 +4629,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>22</v>
@@ -4670,7 +4670,7 @@
         <v>87</v>
       </c>
       <c r="J12" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>22</v>
@@ -4711,7 +4711,7 @@
         <v>93</v>
       </c>
       <c r="J13" s="5">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>22</v>
@@ -4752,7 +4752,7 @@
         <v>99</v>
       </c>
       <c r="J14" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>22</v>
@@ -4793,7 +4793,7 @@
         <v>105</v>
       </c>
       <c r="J15" s="5">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>22</v>
@@ -4834,7 +4834,7 @@
         <v>111</v>
       </c>
       <c r="J16" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>22</v>
@@ -4875,7 +4875,7 @@
         <v>117</v>
       </c>
       <c r="J17" s="5">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>22</v>
@@ -4957,7 +4957,7 @@
         <v>129</v>
       </c>
       <c r="J19" s="5">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>22</v>
@@ -4998,7 +4998,7 @@
         <v>135</v>
       </c>
       <c r="J20" s="2">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>22</v>
@@ -5039,7 +5039,7 @@
         <v>141</v>
       </c>
       <c r="J21" s="5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>22</v>
@@ -5080,7 +5080,7 @@
         <v>149</v>
       </c>
       <c r="J22" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>22</v>
@@ -5121,7 +5121,7 @@
         <v>155</v>
       </c>
       <c r="J23" s="5">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>22</v>
@@ -5162,7 +5162,7 @@
         <v>161</v>
       </c>
       <c r="J24" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>22</v>
@@ -5203,7 +5203,7 @@
         <v>167</v>
       </c>
       <c r="J25" s="5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>22</v>
@@ -5244,7 +5244,7 @@
         <v>173</v>
       </c>
       <c r="J26" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>22</v>
@@ -5285,7 +5285,7 @@
         <v>179</v>
       </c>
       <c r="J27" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>22</v>
@@ -5326,7 +5326,7 @@
         <v>184</v>
       </c>
       <c r="J28" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>22</v>
@@ -5367,7 +5367,7 @@
         <v>190</v>
       </c>
       <c r="J29" s="5">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>22</v>
@@ -5408,7 +5408,7 @@
         <v>196</v>
       </c>
       <c r="J30" s="2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>22</v>
@@ -5449,7 +5449,7 @@
         <v>202</v>
       </c>
       <c r="J31" s="5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>22</v>
@@ -5490,7 +5490,7 @@
         <v>210</v>
       </c>
       <c r="J32" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>22</v>
@@ -5531,7 +5531,7 @@
         <v>216</v>
       </c>
       <c r="J33" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>22</v>
@@ -5572,7 +5572,7 @@
         <v>222</v>
       </c>
       <c r="J34" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>22</v>
@@ -5613,7 +5613,7 @@
         <v>228</v>
       </c>
       <c r="J35" s="5">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>22</v>
@@ -5654,7 +5654,7 @@
         <v>234</v>
       </c>
       <c r="J36" s="2">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>22</v>
@@ -5736,7 +5736,7 @@
         <v>246</v>
       </c>
       <c r="J38" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>22</v>
@@ -5777,7 +5777,7 @@
         <v>252</v>
       </c>
       <c r="J39" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>22</v>
@@ -5818,7 +5818,7 @@
         <v>258</v>
       </c>
       <c r="J40" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>22</v>
@@ -5859,7 +5859,7 @@
         <v>264</v>
       </c>
       <c r="J41" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>22</v>
@@ -5900,7 +5900,7 @@
         <v>272</v>
       </c>
       <c r="J42" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>22</v>
@@ -5941,7 +5941,7 @@
         <v>278</v>
       </c>
       <c r="J43" s="5">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>22</v>
@@ -6023,7 +6023,7 @@
         <v>290</v>
       </c>
       <c r="J45" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>22</v>
@@ -6064,7 +6064,7 @@
         <v>296</v>
       </c>
       <c r="J46" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>22</v>
@@ -6105,7 +6105,7 @@
         <v>302</v>
       </c>
       <c r="J47" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>22</v>
@@ -6146,7 +6146,7 @@
         <v>308</v>
       </c>
       <c r="J48" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>22</v>
@@ -6187,7 +6187,7 @@
         <v>314</v>
       </c>
       <c r="J49" s="5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>22</v>
@@ -6228,7 +6228,7 @@
         <v>320</v>
       </c>
       <c r="J50" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>22</v>
@@ -6269,7 +6269,7 @@
         <v>326</v>
       </c>
       <c r="J51" s="5">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>22</v>
@@ -6351,7 +6351,7 @@
         <v>340</v>
       </c>
       <c r="J53" s="5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>22</v>
@@ -6392,7 +6392,7 @@
         <v>346</v>
       </c>
       <c r="J54" s="2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>22</v>
@@ -6474,7 +6474,7 @@
         <v>358</v>
       </c>
       <c r="J56" s="2">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>22</v>
@@ -6515,7 +6515,7 @@
         <v>364</v>
       </c>
       <c r="J57" s="5">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>22</v>
@@ -6556,7 +6556,7 @@
         <v>370</v>
       </c>
       <c r="J58" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>22</v>
@@ -6597,7 +6597,7 @@
         <v>376</v>
       </c>
       <c r="J59" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>22</v>
@@ -6638,7 +6638,7 @@
         <v>382</v>
       </c>
       <c r="J60" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>22</v>
@@ -6679,7 +6679,7 @@
         <v>388</v>
       </c>
       <c r="J61" s="5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>22</v>
@@ -6720,7 +6720,7 @@
         <v>396</v>
       </c>
       <c r="J62" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>22</v>
@@ -6761,7 +6761,7 @@
         <v>402</v>
       </c>
       <c r="J63" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>22</v>
@@ -6802,7 +6802,7 @@
         <v>408</v>
       </c>
       <c r="J64" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>22</v>
@@ -6843,7 +6843,7 @@
         <v>414</v>
       </c>
       <c r="J65" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>22</v>
@@ -6884,7 +6884,7 @@
         <v>420</v>
       </c>
       <c r="J66" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>22</v>
@@ -6925,7 +6925,7 @@
         <v>426</v>
       </c>
       <c r="J67" s="5">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>22</v>
@@ -6966,7 +6966,7 @@
         <v>432</v>
       </c>
       <c r="J68" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>22</v>
@@ -7007,7 +7007,7 @@
         <v>438</v>
       </c>
       <c r="J69" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>22</v>
@@ -7048,7 +7048,7 @@
         <v>444</v>
       </c>
       <c r="J70" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>22</v>
@@ -7089,7 +7089,7 @@
         <v>450</v>
       </c>
       <c r="J71" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K71" s="4" t="s">
         <v>22</v>
@@ -7171,7 +7171,7 @@
         <v>464</v>
       </c>
       <c r="J73" s="5">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>22</v>
@@ -7212,7 +7212,7 @@
         <v>470</v>
       </c>
       <c r="J74" s="2">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>22</v>
@@ -7253,7 +7253,7 @@
         <v>476</v>
       </c>
       <c r="J75" s="5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>22</v>
@@ -7294,7 +7294,7 @@
         <v>482</v>
       </c>
       <c r="J76" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>22</v>
@@ -7335,7 +7335,7 @@
         <v>488</v>
       </c>
       <c r="J77" s="5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>22</v>
@@ -7376,7 +7376,7 @@
         <v>494</v>
       </c>
       <c r="J78" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>22</v>
@@ -7417,7 +7417,7 @@
         <v>500</v>
       </c>
       <c r="J79" s="5">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>22</v>
@@ -7458,7 +7458,7 @@
         <v>506</v>
       </c>
       <c r="J80" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>22</v>
@@ -7499,7 +7499,7 @@
         <v>512</v>
       </c>
       <c r="J81" s="5">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>22</v>
@@ -7540,7 +7540,7 @@
         <v>520</v>
       </c>
       <c r="J82" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>22</v>
@@ -7581,7 +7581,7 @@
         <v>526</v>
       </c>
       <c r="J83" s="5">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>22</v>
@@ -7622,7 +7622,7 @@
         <v>532</v>
       </c>
       <c r="J84" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>22</v>
@@ -7704,7 +7704,7 @@
         <v>544</v>
       </c>
       <c r="J86" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>22</v>
@@ -7745,7 +7745,7 @@
         <v>550</v>
       </c>
       <c r="J87" s="5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>22</v>
@@ -7786,7 +7786,7 @@
         <v>556</v>
       </c>
       <c r="J88" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>22</v>
@@ -7827,7 +7827,7 @@
         <v>562</v>
       </c>
       <c r="J89" s="5">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>22</v>
@@ -7868,7 +7868,7 @@
         <v>568</v>
       </c>
       <c r="J90" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>22</v>
@@ -7909,7 +7909,7 @@
         <v>574</v>
       </c>
       <c r="J91" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>22</v>
@@ -7950,7 +7950,7 @@
         <v>582</v>
       </c>
       <c r="J92" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>22</v>
@@ -7991,7 +7991,7 @@
         <v>588</v>
       </c>
       <c r="J93" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>22</v>
@@ -8032,7 +8032,7 @@
         <v>594</v>
       </c>
       <c r="J94" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>22</v>
@@ -8073,7 +8073,7 @@
         <v>600</v>
       </c>
       <c r="J95" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>22</v>
@@ -8114,7 +8114,7 @@
         <v>606</v>
       </c>
       <c r="J96" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>22</v>
@@ -8155,7 +8155,7 @@
         <v>612</v>
       </c>
       <c r="J97" s="5">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>22</v>
@@ -8196,7 +8196,7 @@
         <v>618</v>
       </c>
       <c r="J98" s="2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>22</v>
@@ -8237,7 +8237,7 @@
         <v>470</v>
       </c>
       <c r="J99" s="5">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>22</v>
@@ -8278,7 +8278,7 @@
         <v>628</v>
       </c>
       <c r="J100" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>22</v>
@@ -8319,7 +8319,7 @@
         <v>634</v>
       </c>
       <c r="J101" s="5">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>22</v>
@@ -8360,7 +8360,7 @@
         <v>21</v>
       </c>
       <c r="J102" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>22</v>
@@ -8401,7 +8401,7 @@
         <v>29</v>
       </c>
       <c r="J103" s="5">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>22</v>
@@ -8442,7 +8442,7 @@
         <v>36</v>
       </c>
       <c r="J104" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>22</v>
@@ -8483,7 +8483,7 @@
         <v>42</v>
       </c>
       <c r="J105" s="5">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>22</v>
@@ -8524,7 +8524,7 @@
         <v>49</v>
       </c>
       <c r="J106" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>22</v>
@@ -8565,7 +8565,7 @@
         <v>55</v>
       </c>
       <c r="J107" s="5">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>22</v>
@@ -8606,7 +8606,7 @@
         <v>61</v>
       </c>
       <c r="J108" s="2">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>22</v>
@@ -8647,7 +8647,7 @@
         <v>67</v>
       </c>
       <c r="J109" s="5">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>22</v>
@@ -8688,7 +8688,7 @@
         <v>73</v>
       </c>
       <c r="J110" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>22</v>
@@ -8729,7 +8729,7 @@
         <v>79</v>
       </c>
       <c r="J111" s="5">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>22</v>
@@ -8770,7 +8770,7 @@
         <v>87</v>
       </c>
       <c r="J112" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>22</v>
@@ -8852,7 +8852,7 @@
         <v>99</v>
       </c>
       <c r="J114" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>22</v>
@@ -8893,7 +8893,7 @@
         <v>105</v>
       </c>
       <c r="J115" s="5">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>22</v>
@@ -8934,7 +8934,7 @@
         <v>111</v>
       </c>
       <c r="J116" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>22</v>
@@ -8975,7 +8975,7 @@
         <v>117</v>
       </c>
       <c r="J117" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>22</v>
@@ -9016,7 +9016,7 @@
         <v>123</v>
       </c>
       <c r="J118" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>22</v>
@@ -9057,7 +9057,7 @@
         <v>129</v>
       </c>
       <c r="J119" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>22</v>
@@ -9098,7 +9098,7 @@
         <v>135</v>
       </c>
       <c r="J120" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>22</v>
@@ -9139,7 +9139,7 @@
         <v>141</v>
       </c>
       <c r="J121" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>22</v>
@@ -9180,7 +9180,7 @@
         <v>149</v>
       </c>
       <c r="J122" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>22</v>
@@ -9262,7 +9262,7 @@
         <v>161</v>
       </c>
       <c r="J124" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>22</v>
@@ -9303,7 +9303,7 @@
         <v>167</v>
       </c>
       <c r="J125" s="5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>22</v>
@@ -9344,7 +9344,7 @@
         <v>173</v>
       </c>
       <c r="J126" s="2">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>22</v>
@@ -9385,7 +9385,7 @@
         <v>179</v>
       </c>
       <c r="J127" s="5">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>22</v>
@@ -9426,7 +9426,7 @@
         <v>184</v>
       </c>
       <c r="J128" s="2">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>22</v>
@@ -9467,7 +9467,7 @@
         <v>190</v>
       </c>
       <c r="J129" s="5">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>22</v>
@@ -9508,7 +9508,7 @@
         <v>196</v>
       </c>
       <c r="J130" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>22</v>
@@ -9549,7 +9549,7 @@
         <v>202</v>
       </c>
       <c r="J131" s="5">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>22</v>
@@ -9590,7 +9590,7 @@
         <v>210</v>
       </c>
       <c r="J132" s="2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>22</v>
@@ -9631,7 +9631,7 @@
         <v>216</v>
       </c>
       <c r="J133" s="5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>22</v>
@@ -9672,7 +9672,7 @@
         <v>222</v>
       </c>
       <c r="J134" s="2">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>22</v>
@@ -9754,7 +9754,7 @@
         <v>234</v>
       </c>
       <c r="J136" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>22</v>
@@ -9795,7 +9795,7 @@
         <v>240</v>
       </c>
       <c r="J137" s="5">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>22</v>
@@ -9836,7 +9836,7 @@
         <v>246</v>
       </c>
       <c r="J138" s="2">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>22</v>
@@ -9877,7 +9877,7 @@
         <v>252</v>
       </c>
       <c r="J139" s="5">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>22</v>
@@ -9918,7 +9918,7 @@
         <v>258</v>
       </c>
       <c r="J140" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>22</v>
@@ -9959,7 +9959,7 @@
         <v>264</v>
       </c>
       <c r="J141" s="5">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>22</v>
@@ -10000,7 +10000,7 @@
         <v>272</v>
       </c>
       <c r="J142" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>22</v>
@@ -10041,7 +10041,7 @@
         <v>278</v>
       </c>
       <c r="J143" s="5">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>22</v>
@@ -10082,7 +10082,7 @@
         <v>284</v>
       </c>
       <c r="J144" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>22</v>
@@ -10123,7 +10123,7 @@
         <v>290</v>
       </c>
       <c r="J145" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>22</v>
@@ -10164,7 +10164,7 @@
         <v>296</v>
       </c>
       <c r="J146" s="2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>22</v>
@@ -10205,7 +10205,7 @@
         <v>302</v>
       </c>
       <c r="J147" s="5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>22</v>
@@ -10246,7 +10246,7 @@
         <v>308</v>
       </c>
       <c r="J148" s="2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>22</v>
@@ -10287,7 +10287,7 @@
         <v>314</v>
       </c>
       <c r="J149" s="5">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>22</v>
@@ -10328,7 +10328,7 @@
         <v>320</v>
       </c>
       <c r="J150" s="2">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>22</v>
@@ -10369,7 +10369,7 @@
         <v>326</v>
       </c>
       <c r="J151" s="5">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>22</v>
@@ -10410,7 +10410,7 @@
         <v>334</v>
       </c>
       <c r="J152" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>22</v>
@@ -10451,7 +10451,7 @@
         <v>340</v>
       </c>
       <c r="J153" s="5">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>22</v>
@@ -10492,7 +10492,7 @@
         <v>346</v>
       </c>
       <c r="J154" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>22</v>
@@ -10533,7 +10533,7 @@
         <v>352</v>
       </c>
       <c r="J155" s="5">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>22</v>
@@ -10574,7 +10574,7 @@
         <v>358</v>
       </c>
       <c r="J156" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>22</v>
@@ -10615,7 +10615,7 @@
         <v>364</v>
       </c>
       <c r="J157" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>22</v>
@@ -10656,7 +10656,7 @@
         <v>370</v>
       </c>
       <c r="J158" s="2">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>22</v>
@@ -10697,7 +10697,7 @@
         <v>376</v>
       </c>
       <c r="J159" s="5">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>22</v>
@@ -10738,7 +10738,7 @@
         <v>382</v>
       </c>
       <c r="J160" s="2">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>22</v>
@@ -10779,7 +10779,7 @@
         <v>388</v>
       </c>
       <c r="J161" s="5">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>22</v>
@@ -10820,7 +10820,7 @@
         <v>396</v>
       </c>
       <c r="J162" s="2">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>22</v>
@@ -10861,7 +10861,7 @@
         <v>402</v>
       </c>
       <c r="J163" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>22</v>
@@ -10902,7 +10902,7 @@
         <v>408</v>
       </c>
       <c r="J164" s="2">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>22</v>
@@ -10984,7 +10984,7 @@
         <v>420</v>
       </c>
       <c r="J166" s="2">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>22</v>
@@ -11025,7 +11025,7 @@
         <v>426</v>
       </c>
       <c r="J167" s="5">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>22</v>
@@ -11066,7 +11066,7 @@
         <v>432</v>
       </c>
       <c r="J168" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>22</v>
@@ -11107,7 +11107,7 @@
         <v>438</v>
       </c>
       <c r="J169" s="5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>22</v>
@@ -11148,7 +11148,7 @@
         <v>444</v>
       </c>
       <c r="J170" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>22</v>
@@ -11189,7 +11189,7 @@
         <v>450</v>
       </c>
       <c r="J171" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>22</v>
@@ -11230,7 +11230,7 @@
         <v>458</v>
       </c>
       <c r="J172" s="2">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>22</v>
@@ -11271,7 +11271,7 @@
         <v>464</v>
       </c>
       <c r="J173" s="5">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K173" s="4" t="s">
         <v>22</v>
@@ -11312,7 +11312,7 @@
         <v>470</v>
       </c>
       <c r="J174" s="2">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>22</v>
@@ -11353,7 +11353,7 @@
         <v>476</v>
       </c>
       <c r="J175" s="5">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>22</v>
@@ -11394,7 +11394,7 @@
         <v>482</v>
       </c>
       <c r="J176" s="2">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>22</v>
@@ -11435,7 +11435,7 @@
         <v>488</v>
       </c>
       <c r="J177" s="5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>22</v>
@@ -11476,7 +11476,7 @@
         <v>494</v>
       </c>
       <c r="J178" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>22</v>
@@ -11517,7 +11517,7 @@
         <v>500</v>
       </c>
       <c r="J179" s="5">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>22</v>
@@ -11558,7 +11558,7 @@
         <v>506</v>
       </c>
       <c r="J180" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>22</v>
@@ -11599,7 +11599,7 @@
         <v>512</v>
       </c>
       <c r="J181" s="5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>22</v>
@@ -11640,7 +11640,7 @@
         <v>520</v>
       </c>
       <c r="J182" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>22</v>
@@ -11681,7 +11681,7 @@
         <v>526</v>
       </c>
       <c r="J183" s="5">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>22</v>
@@ -11722,7 +11722,7 @@
         <v>532</v>
       </c>
       <c r="J184" s="2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K184" s="4" t="s">
         <v>22</v>
@@ -11763,7 +11763,7 @@
         <v>538</v>
       </c>
       <c r="J185" s="5">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>22</v>
@@ -11804,7 +11804,7 @@
         <v>544</v>
       </c>
       <c r="J186" s="2">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>22</v>
@@ -11845,7 +11845,7 @@
         <v>550</v>
       </c>
       <c r="J187" s="5">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>22</v>
@@ -11886,7 +11886,7 @@
         <v>556</v>
       </c>
       <c r="J188" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>22</v>
@@ -11927,7 +11927,7 @@
         <v>562</v>
       </c>
       <c r="J189" s="5">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>22</v>
@@ -11968,7 +11968,7 @@
         <v>568</v>
       </c>
       <c r="J190" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>22</v>
@@ -12009,7 +12009,7 @@
         <v>574</v>
       </c>
       <c r="J191" s="5">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>22</v>
@@ -12050,7 +12050,7 @@
         <v>582</v>
       </c>
       <c r="J192" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>22</v>
@@ -12091,7 +12091,7 @@
         <v>588</v>
       </c>
       <c r="J193" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>22</v>
@@ -12132,7 +12132,7 @@
         <v>594</v>
       </c>
       <c r="J194" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K194" s="4" t="s">
         <v>22</v>
@@ -12214,7 +12214,7 @@
         <v>606</v>
       </c>
       <c r="J196" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>22</v>
@@ -12296,7 +12296,7 @@
         <v>618</v>
       </c>
       <c r="J198" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K198" s="4" t="s">
         <v>22</v>
@@ -12337,7 +12337,7 @@
         <v>470</v>
       </c>
       <c r="J199" s="5">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>22</v>
@@ -12378,7 +12378,7 @@
         <v>628</v>
       </c>
       <c r="J200" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>22</v>
@@ -12419,7 +12419,7 @@
         <v>634</v>
       </c>
       <c r="J201" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>22</v>
@@ -12460,7 +12460,7 @@
         <v>21</v>
       </c>
       <c r="J202" s="2">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>22</v>
@@ -12501,7 +12501,7 @@
         <v>29</v>
       </c>
       <c r="J203" s="5">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K203" s="4" t="s">
         <v>22</v>
@@ -12583,7 +12583,7 @@
         <v>42</v>
       </c>
       <c r="J205" s="5">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K205" s="4" t="s">
         <v>22</v>
@@ -12624,7 +12624,7 @@
         <v>49</v>
       </c>
       <c r="J206" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>22</v>
@@ -12665,7 +12665,7 @@
         <v>55</v>
       </c>
       <c r="J207" s="5">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="K207" s="4" t="s">
         <v>22</v>
@@ -12706,7 +12706,7 @@
         <v>61</v>
       </c>
       <c r="J208" s="2">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>22</v>
@@ -12747,7 +12747,7 @@
         <v>67</v>
       </c>
       <c r="J209" s="5">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>22</v>
@@ -12788,7 +12788,7 @@
         <v>73</v>
       </c>
       <c r="J210" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>22</v>
@@ -12829,7 +12829,7 @@
         <v>79</v>
       </c>
       <c r="J211" s="5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>22</v>
@@ -12870,7 +12870,7 @@
         <v>87</v>
       </c>
       <c r="J212" s="2">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>22</v>
@@ -12911,7 +12911,7 @@
         <v>93</v>
       </c>
       <c r="J213" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K213" s="4" t="s">
         <v>22</v>
@@ -12952,7 +12952,7 @@
         <v>99</v>
       </c>
       <c r="J214" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>22</v>
@@ -12993,7 +12993,7 @@
         <v>105</v>
       </c>
       <c r="J215" s="5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K215" s="4" t="s">
         <v>22</v>
@@ -13034,7 +13034,7 @@
         <v>111</v>
       </c>
       <c r="J216" s="2">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>22</v>
@@ -13075,7 +13075,7 @@
         <v>117</v>
       </c>
       <c r="J217" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>22</v>
@@ -13116,7 +13116,7 @@
         <v>123</v>
       </c>
       <c r="J218" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K218" s="4" t="s">
         <v>22</v>
@@ -13157,7 +13157,7 @@
         <v>129</v>
       </c>
       <c r="J219" s="5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K219" s="4" t="s">
         <v>22</v>
@@ -13198,7 +13198,7 @@
         <v>135</v>
       </c>
       <c r="J220" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>22</v>
@@ -13239,7 +13239,7 @@
         <v>141</v>
       </c>
       <c r="J221" s="5">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="K221" s="4" t="s">
         <v>22</v>
@@ -13280,7 +13280,7 @@
         <v>149</v>
       </c>
       <c r="J222" s="2">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K222" s="4" t="s">
         <v>22</v>
@@ -13321,7 +13321,7 @@
         <v>155</v>
       </c>
       <c r="J223" s="5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K223" s="4" t="s">
         <v>22</v>
@@ -13362,7 +13362,7 @@
         <v>161</v>
       </c>
       <c r="J224" s="2">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>22</v>
@@ -13403,7 +13403,7 @@
         <v>167</v>
       </c>
       <c r="J225" s="5">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>22</v>
@@ -13444,7 +13444,7 @@
         <v>173</v>
       </c>
       <c r="J226" s="2">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K226" s="4" t="s">
         <v>22</v>
@@ -13485,7 +13485,7 @@
         <v>179</v>
       </c>
       <c r="J227" s="5">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>22</v>
@@ -13526,7 +13526,7 @@
         <v>184</v>
       </c>
       <c r="J228" s="2">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>22</v>
@@ -13567,7 +13567,7 @@
         <v>190</v>
       </c>
       <c r="J229" s="5">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K229" s="4" t="s">
         <v>22</v>
@@ -13608,7 +13608,7 @@
         <v>196</v>
       </c>
       <c r="J230" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K230" s="4" t="s">
         <v>22</v>
@@ -13649,7 +13649,7 @@
         <v>202</v>
       </c>
       <c r="J231" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K231" s="4" t="s">
         <v>22</v>
@@ -13690,7 +13690,7 @@
         <v>210</v>
       </c>
       <c r="J232" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K232" s="4" t="s">
         <v>22</v>
@@ -13731,7 +13731,7 @@
         <v>216</v>
       </c>
       <c r="J233" s="5">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="K233" s="4" t="s">
         <v>22</v>
@@ -13772,7 +13772,7 @@
         <v>222</v>
       </c>
       <c r="J234" s="2">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K234" s="4" t="s">
         <v>22</v>
@@ -13813,7 +13813,7 @@
         <v>228</v>
       </c>
       <c r="J235" s="5">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="K235" s="4" t="s">
         <v>22</v>
@@ -13854,7 +13854,7 @@
         <v>234</v>
       </c>
       <c r="J236" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K236" s="4" t="s">
         <v>22</v>
@@ -13895,7 +13895,7 @@
         <v>240</v>
       </c>
       <c r="J237" s="5">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K237" s="4" t="s">
         <v>22</v>
@@ -13936,7 +13936,7 @@
         <v>246</v>
       </c>
       <c r="J238" s="2">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>22</v>
@@ -13977,7 +13977,7 @@
         <v>252</v>
       </c>
       <c r="J239" s="5">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>22</v>
@@ -14018,7 +14018,7 @@
         <v>258</v>
       </c>
       <c r="J240" s="2">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="K240" s="4" t="s">
         <v>22</v>
@@ -14059,7 +14059,7 @@
         <v>264</v>
       </c>
       <c r="J241" s="5">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K241" s="4" t="s">
         <v>22</v>
@@ -14100,7 +14100,7 @@
         <v>272</v>
       </c>
       <c r="J242" s="2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>22</v>
@@ -14141,7 +14141,7 @@
         <v>278</v>
       </c>
       <c r="J243" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>22</v>
@@ -14182,7 +14182,7 @@
         <v>284</v>
       </c>
       <c r="J244" s="2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>22</v>
@@ -14223,7 +14223,7 @@
         <v>290</v>
       </c>
       <c r="J245" s="5">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K245" s="4" t="s">
         <v>22</v>
@@ -14264,7 +14264,7 @@
         <v>296</v>
       </c>
       <c r="J246" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>22</v>
@@ -14305,7 +14305,7 @@
         <v>302</v>
       </c>
       <c r="J247" s="5">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="K247" s="4" t="s">
         <v>22</v>
@@ -14346,7 +14346,7 @@
         <v>308</v>
       </c>
       <c r="J248" s="2">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K248" s="4" t="s">
         <v>22</v>
@@ -14387,7 +14387,7 @@
         <v>314</v>
       </c>
       <c r="J249" s="5">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="K249" s="4" t="s">
         <v>22</v>
@@ -14428,7 +14428,7 @@
         <v>320</v>
       </c>
       <c r="J250" s="2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>22</v>
@@ -14469,7 +14469,7 @@
         <v>326</v>
       </c>
       <c r="J251" s="5">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="K251" s="4" t="s">
         <v>22</v>
@@ -14510,7 +14510,7 @@
         <v>334</v>
       </c>
       <c r="J252" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K252" s="4" t="s">
         <v>22</v>
@@ -14551,7 +14551,7 @@
         <v>340</v>
       </c>
       <c r="J253" s="5">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>22</v>
@@ -14592,7 +14592,7 @@
         <v>346</v>
       </c>
       <c r="J254" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K254" s="4" t="s">
         <v>22</v>
@@ -14633,7 +14633,7 @@
         <v>352</v>
       </c>
       <c r="J255" s="5">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K255" s="4" t="s">
         <v>22</v>
@@ -14674,7 +14674,7 @@
         <v>358</v>
       </c>
       <c r="J256" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>22</v>
@@ -14715,7 +14715,7 @@
         <v>364</v>
       </c>
       <c r="J257" s="5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K257" s="4" t="s">
         <v>22</v>
@@ -14756,7 +14756,7 @@
         <v>370</v>
       </c>
       <c r="J258" s="2">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>22</v>
@@ -14797,7 +14797,7 @@
         <v>376</v>
       </c>
       <c r="J259" s="5">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>22</v>
@@ -14838,7 +14838,7 @@
         <v>382</v>
       </c>
       <c r="J260" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>22</v>
@@ -14879,7 +14879,7 @@
         <v>388</v>
       </c>
       <c r="J261" s="5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>22</v>
@@ -14920,7 +14920,7 @@
         <v>396</v>
       </c>
       <c r="J262" s="2">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>22</v>
@@ -14961,7 +14961,7 @@
         <v>402</v>
       </c>
       <c r="J263" s="5">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>22</v>
@@ -15002,7 +15002,7 @@
         <v>408</v>
       </c>
       <c r="J264" s="2">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="K264" s="4" t="s">
         <v>22</v>
@@ -15043,7 +15043,7 @@
         <v>414</v>
       </c>
       <c r="J265" s="5">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K265" s="4" t="s">
         <v>22</v>
@@ -15084,7 +15084,7 @@
         <v>420</v>
       </c>
       <c r="J266" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>22</v>
@@ -15125,7 +15125,7 @@
         <v>426</v>
       </c>
       <c r="J267" s="5">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K267" s="4" t="s">
         <v>22</v>
@@ -15166,7 +15166,7 @@
         <v>432</v>
       </c>
       <c r="J268" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K268" s="4" t="s">
         <v>22</v>
@@ -15207,7 +15207,7 @@
         <v>438</v>
       </c>
       <c r="J269" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>22</v>
@@ -15248,7 +15248,7 @@
         <v>444</v>
       </c>
       <c r="J270" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K270" s="4" t="s">
         <v>22</v>
@@ -15289,7 +15289,7 @@
         <v>450</v>
       </c>
       <c r="J271" s="5">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="K271" s="4" t="s">
         <v>22</v>
@@ -15330,7 +15330,7 @@
         <v>458</v>
       </c>
       <c r="J272" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>22</v>
@@ -15371,7 +15371,7 @@
         <v>464</v>
       </c>
       <c r="J273" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K273" s="4" t="s">
         <v>22</v>
@@ -15412,7 +15412,7 @@
         <v>470</v>
       </c>
       <c r="J274" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K274" s="4" t="s">
         <v>22</v>
@@ -15453,7 +15453,7 @@
         <v>476</v>
       </c>
       <c r="J275" s="5">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="K275" s="4" t="s">
         <v>22</v>
@@ -15494,7 +15494,7 @@
         <v>482</v>
       </c>
       <c r="J276" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>22</v>
@@ -15535,7 +15535,7 @@
         <v>488</v>
       </c>
       <c r="J277" s="5">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>22</v>
@@ -15576,7 +15576,7 @@
         <v>494</v>
       </c>
       <c r="J278" s="2">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="K278" s="4" t="s">
         <v>22</v>
@@ -15617,7 +15617,7 @@
         <v>500</v>
       </c>
       <c r="J279" s="5">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K279" s="4" t="s">
         <v>22</v>
@@ -15658,7 +15658,7 @@
         <v>506</v>
       </c>
       <c r="J280" s="2">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>22</v>
@@ -15699,7 +15699,7 @@
         <v>512</v>
       </c>
       <c r="J281" s="5">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>22</v>
@@ -15740,7 +15740,7 @@
         <v>520</v>
       </c>
       <c r="J282" s="2">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>22</v>
@@ -15781,7 +15781,7 @@
         <v>526</v>
       </c>
       <c r="J283" s="5">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K283" s="4" t="s">
         <v>22</v>
@@ -15822,7 +15822,7 @@
         <v>532</v>
       </c>
       <c r="J284" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K284" s="4" t="s">
         <v>22</v>
@@ -15863,7 +15863,7 @@
         <v>538</v>
       </c>
       <c r="J285" s="5">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>22</v>
@@ -15904,7 +15904,7 @@
         <v>544</v>
       </c>
       <c r="J286" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K286" s="4" t="s">
         <v>22</v>
@@ -15945,7 +15945,7 @@
         <v>550</v>
       </c>
       <c r="J287" s="5">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K287" s="4" t="s">
         <v>22</v>
@@ -15986,7 +15986,7 @@
         <v>556</v>
       </c>
       <c r="J288" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K288" s="4" t="s">
         <v>22</v>
@@ -16027,7 +16027,7 @@
         <v>562</v>
       </c>
       <c r="J289" s="5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K289" s="4" t="s">
         <v>22</v>
@@ -16068,7 +16068,7 @@
         <v>568</v>
       </c>
       <c r="J290" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K290" s="4" t="s">
         <v>22</v>
@@ -16109,7 +16109,7 @@
         <v>574</v>
       </c>
       <c r="J291" s="5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K291" s="4" t="s">
         <v>22</v>
@@ -16150,7 +16150,7 @@
         <v>582</v>
       </c>
       <c r="J292" s="2">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="K292" s="4" t="s">
         <v>22</v>
@@ -16191,7 +16191,7 @@
         <v>588</v>
       </c>
       <c r="J293" s="5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>22</v>
@@ -16232,7 +16232,7 @@
         <v>594</v>
       </c>
       <c r="J294" s="2">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>22</v>
@@ -16273,7 +16273,7 @@
         <v>600</v>
       </c>
       <c r="J295" s="5">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K295" s="4" t="s">
         <v>22</v>
@@ -16314,7 +16314,7 @@
         <v>606</v>
       </c>
       <c r="J296" s="2">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K296" s="4" t="s">
         <v>22</v>
@@ -16396,7 +16396,7 @@
         <v>618</v>
       </c>
       <c r="J298" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K298" s="4" t="s">
         <v>22</v>
@@ -16437,7 +16437,7 @@
         <v>470</v>
       </c>
       <c r="J299" s="5">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K299" s="4" t="s">
         <v>22</v>
@@ -16478,7 +16478,7 @@
         <v>628</v>
       </c>
       <c r="J300" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K300" s="4" t="s">
         <v>22</v>
@@ -16519,7 +16519,7 @@
         <v>634</v>
       </c>
       <c r="J301" s="5">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>22</v>
